--- a/Diagramme/SmartClock_Gantt-Diagramm_V2.xlsx
+++ b/Diagramme/SmartClock_Gantt-Diagramm_V2.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="652" documentId="8_{0C4EAEB1-A5C4-4402-980F-B32D81185735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FDE7375-5207-471D-9742-F09B0126406A}"/>
+  <xr:revisionPtr revIDLastSave="664" documentId="8_{0C4EAEB1-A5C4-4402-980F-B32D81185735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98B27C84-C4C2-4BB9-B97A-BDE1A1E0F90D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="415" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="415" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="12" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="67">
   <si>
     <t>INFORMATIONEN ZU DIESEM GANTT-DIAGRAMM</t>
   </si>
@@ -266,6 +266,15 @@
   </si>
   <si>
     <t>2h</t>
+  </si>
+  <si>
+    <t>Joystick gestures</t>
+  </si>
+  <si>
+    <t>Set Timer using Joystick</t>
+  </si>
+  <si>
+    <t>7h</t>
   </si>
 </sst>
 </file>
@@ -1187,6 +1196,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="13" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1244,9 +1256,6 @@
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Akzent3" xfId="11" builtinId="37"/>
@@ -1262,231 +1271,7 @@
     <cellStyle name="Überschrift 3" xfId="8" builtinId="18" customBuiltin="1"/>
     <cellStyle name="zAusgeblText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="111">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="56">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1630,420 +1415,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <color theme="0"/>
       </font>
@@ -2129,141 +1500,20 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
       <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
+        <left style="thin">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFC00000"/>
+        </right>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2788,21 +2038,21 @@
   </dxfs>
   <tableStyles count="2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Gantt-Tabellenformat" pivot="0" count="4" xr9:uid="{4904D139-63E4-4221-B7C9-C6C5B7A50FAF}">
-      <tableStyleElement type="wholeTable" dxfId="110"/>
-      <tableStyleElement type="headerRow" dxfId="109"/>
-      <tableStyleElement type="firstRowStripe" dxfId="108"/>
-      <tableStyleElement type="secondRowStripe" dxfId="107"/>
+      <tableStyleElement type="wholeTable" dxfId="55"/>
+      <tableStyleElement type="headerRow" dxfId="54"/>
+      <tableStyleElement type="firstRowStripe" dxfId="53"/>
+      <tableStyleElement type="secondRowStripe" dxfId="52"/>
     </tableStyle>
     <tableStyle name="Aufgabenliste" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="106"/>
-      <tableStyleElement type="headerRow" dxfId="105"/>
-      <tableStyleElement type="totalRow" dxfId="104"/>
-      <tableStyleElement type="firstColumn" dxfId="103"/>
-      <tableStyleElement type="lastColumn" dxfId="102"/>
-      <tableStyleElement type="firstRowStripe" dxfId="101"/>
-      <tableStyleElement type="secondRowStripe" dxfId="100"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="99"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="98"/>
+      <tableStyleElement type="wholeTable" dxfId="51"/>
+      <tableStyleElement type="headerRow" dxfId="50"/>
+      <tableStyleElement type="totalRow" dxfId="49"/>
+      <tableStyleElement type="firstColumn" dxfId="48"/>
+      <tableStyleElement type="lastColumn" dxfId="47"/>
+      <tableStyleElement type="firstRowStripe" dxfId="46"/>
+      <tableStyleElement type="secondRowStripe" dxfId="45"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="44"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="43"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -2954,7 +2204,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Meilensteine4352" displayName="Meilensteine4352" ref="B9:G36" totalsRowShown="0" headerRowDxfId="97" dataDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Meilensteine4352" displayName="Meilensteine4352" ref="B9:G36" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2964,12 +2214,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Meilensteinbeschreibung" dataDxfId="95"/>
-    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Kategorie" dataDxfId="94"/>
-    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Zeitaufwand in std" dataDxfId="93"/>
-    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Fortschritt" dataDxfId="92"/>
-    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Start" dataDxfId="91" dataCellStyle="Datum"/>
-    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Tage" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Meilensteinbeschreibung" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Kategorie" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Zeitaufwand in std" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Fortschritt" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Start" dataDxfId="36" dataCellStyle="Datum"/>
+    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Tage" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="Aufgabenliste" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -2981,7 +2231,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Meilensteine435" displayName="Meilensteine435" ref="B9:G36" totalsRowShown="0" headerRowDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Meilensteine435" displayName="Meilensteine435" ref="B9:G36" totalsRowShown="0" headerRowDxfId="34">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2991,9 +2241,9 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Meilensteinbeschreibung" dataDxfId="88"/>
-    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Kategorie" dataDxfId="87"/>
-    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Aufwand Soll / Ist" dataDxfId="86"/>
+    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Meilensteinbeschreibung" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Kategorie" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Aufwand Soll / Ist" dataDxfId="31"/>
     <tableColumn id="4" xr3:uid="{62B00BEF-16BE-4692-B5E2-F287F680F2C1}" name="Fortschritt"/>
     <tableColumn id="5" xr3:uid="{D6D72902-F68F-4E59-A714-AFFF520C647A}" name="Start" dataCellStyle="Datum"/>
     <tableColumn id="6" xr3:uid="{93E698DE-286F-49ED-AA20-D0C843671DE8}" name="Tage"/>
@@ -3008,7 +2258,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Meilensteine43524" displayName="Meilensteine43524" ref="B9:G36" totalsRowShown="0" headerRowDxfId="85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Meilensteine43524" displayName="Meilensteine43524" ref="B9:G36" totalsRowShown="0" headerRowDxfId="30">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3018,9 +2268,9 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0971B905-713A-4980-8BBC-DF959C2E61F9}" name="Meilensteinbeschreibung" dataDxfId="84"/>
-    <tableColumn id="2" xr3:uid="{4492A0B8-068F-4002-9E8D-E1F5FED367F0}" name="Kategorie" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{DF1A764E-7050-4528-B7F9-B6AB99372146}" name="Zugewiesen zu" dataDxfId="82"/>
+    <tableColumn id="1" xr3:uid="{0971B905-713A-4980-8BBC-DF959C2E61F9}" name="Meilensteinbeschreibung" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{4492A0B8-068F-4002-9E8D-E1F5FED367F0}" name="Kategorie" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{DF1A764E-7050-4528-B7F9-B6AB99372146}" name="Zugewiesen zu" dataDxfId="27"/>
     <tableColumn id="4" xr3:uid="{47C54592-75B0-4C70-BBF8-0F40483670E9}" name="Fortschritt"/>
     <tableColumn id="5" xr3:uid="{663FB5E0-7616-4EA5-B56A-FF069E2E07D7}" name="Start" dataCellStyle="Datum"/>
     <tableColumn id="6" xr3:uid="{3B766962-C06F-4E12-BE91-12AB93439874}" name="Tage"/>
@@ -3299,26 +2549,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="8" customWidth="1"/>
-    <col min="3" max="5" width="40.7109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="1" width="4.73046875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="2.73046875" style="8" customWidth="1"/>
+    <col min="3" max="5" width="40.73046875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="2.73046875" style="6" customWidth="1"/>
+    <col min="7" max="16384" width="9.1328125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" ht="28.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" s="7" customFormat="1" ht="28.5" x14ac:dyDescent="0.75">
       <c r="D1" s="104"/>
     </row>
-    <row r="2" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" s="7"/>
       <c r="B2" s="110"/>
-      <c r="C2" s="124" t="s">
+      <c r="C2" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
       <c r="F2" s="110"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -3328,7 +2578,7 @@
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
     </row>
-    <row r="3" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A3" s="7"/>
       <c r="B3" s="105"/>
       <c r="C3" s="106"/>
@@ -3343,14 +2593,14 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A4" s="7"/>
       <c r="B4" s="105"/>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="126"/>
       <c r="F4" s="105"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -3360,14 +2610,14 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A5" s="7"/>
       <c r="B5" s="105"/>
-      <c r="C5" s="125" t="s">
+      <c r="C5" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
       <c r="F5" s="105"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -3377,7 +2627,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="108"/>
       <c r="C6" s="108"/>
@@ -3385,15 +2635,15 @@
       <c r="E6" s="108"/>
       <c r="F6" s="108"/>
     </row>
-    <row r="7" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
     </row>
-    <row r="8" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
     </row>
-    <row r="9" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -3401,51 +2651,51 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="D18" s="8"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="D19" s="8"/>
@@ -3468,44 +2718,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="9" max="64" width="3.5703125" customWidth="1"/>
-    <col min="65" max="65" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.73046875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="37.86328125" customWidth="1"/>
+    <col min="3" max="3" width="15.265625" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" customWidth="1"/>
+    <col min="5" max="5" width="15.73046875" customWidth="1"/>
+    <col min="6" max="6" width="10.3984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.3984375" customWidth="1"/>
+    <col min="8" max="8" width="2.73046875" customWidth="1"/>
+    <col min="9" max="64" width="3.59765625" customWidth="1"/>
+    <col min="65" max="65" width="2.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="10"/>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="129"/>
-      <c r="S2" s="129"/>
-      <c r="T2" s="129"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="130"/>
+      <c r="P2" s="130"/>
+      <c r="Q2" s="130"/>
+      <c r="R2" s="130"/>
+      <c r="S2" s="130"/>
+      <c r="T2" s="130"/>
       <c r="U2" s="64"/>
       <c r="V2" s="64"/>
       <c r="W2" s="64"/>
@@ -3552,7 +2802,7 @@
       <c r="BL2" s="64"/>
       <c r="BM2" s="64"/>
     </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="10"/>
       <c r="B3" s="65"/>
       <c r="C3" s="66"/>
@@ -3566,7 +2816,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="10"/>
       <c r="B4" s="69" t="s">
         <v>36</v>
@@ -3579,40 +2829,40 @@
         <v>30</v>
       </c>
       <c r="H4" s="72"/>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="131"/>
-      <c r="T4" s="131"/>
-      <c r="U4" s="131"/>
-      <c r="W4" s="131"/>
-      <c r="X4" s="131"/>
-      <c r="Y4" s="131"/>
-      <c r="Z4" s="131"/>
-      <c r="AA4" s="131"/>
-      <c r="AB4" s="131"/>
-      <c r="AD4" s="131"/>
-      <c r="AE4" s="131"/>
-      <c r="AF4" s="131"/>
-      <c r="AG4" s="131"/>
-      <c r="AH4" s="131"/>
-      <c r="AJ4" s="126"/>
-      <c r="AK4" s="126"/>
-      <c r="AL4" s="126"/>
-      <c r="AM4" s="126"/>
-      <c r="AN4" s="126"/>
-      <c r="AO4" s="126"/>
-      <c r="AP4" s="126"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="131"/>
+      <c r="P4" s="132"/>
+      <c r="Q4" s="132"/>
+      <c r="R4" s="132"/>
+      <c r="S4" s="132"/>
+      <c r="T4" s="132"/>
+      <c r="U4" s="132"/>
+      <c r="W4" s="132"/>
+      <c r="X4" s="132"/>
+      <c r="Y4" s="132"/>
+      <c r="Z4" s="132"/>
+      <c r="AA4" s="132"/>
+      <c r="AB4" s="132"/>
+      <c r="AD4" s="132"/>
+      <c r="AE4" s="132"/>
+      <c r="AF4" s="132"/>
+      <c r="AG4" s="132"/>
+      <c r="AH4" s="132"/>
+      <c r="AJ4" s="127"/>
+      <c r="AK4" s="127"/>
+      <c r="AL4" s="127"/>
+      <c r="AM4" s="127"/>
+      <c r="AN4" s="127"/>
+      <c r="AO4" s="127"/>
+      <c r="AP4" s="127"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
@@ -3626,7 +2876,7 @@
       <c r="G5" s="72"/>
       <c r="H5" s="72"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A6" s="10"/>
       <c r="B6" s="76" t="s">
         <v>6</v>
@@ -3720,7 +2970,7 @@
       <c r="BK6" s="87"/>
       <c r="BL6" s="87"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="10"/>
       <c r="B7" s="76" t="s">
         <v>7</v>
@@ -3958,7 +3208,7 @@
         <v>46021</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="10"/>
       <c r="B8" s="71"/>
       <c r="C8" s="71"/>
@@ -4024,7 +3274,7 @@
       <c r="BK8" s="99"/>
       <c r="BL8" s="102"/>
     </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
@@ -4272,7 +3522,7 @@
         <v>D</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="16"/>
       <c r="C10" s="13"/>
       <c r="D10" s="12"/>
@@ -4336,7 +3586,7 @@
       <c r="BK10" s="34"/>
       <c r="BL10" s="34"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="123" t="s">
         <v>43</v>
@@ -4581,7 +3831,7 @@
       </c>
       <c r="BP11" s="39"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="10"/>
       <c r="B12" s="123"/>
       <c r="C12" s="57" t="s">
@@ -4823,7 +4073,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="10"/>
       <c r="B13" s="123" t="s">
         <v>44</v>
@@ -5067,7 +4317,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="9"/>
       <c r="B14" s="123"/>
       <c r="C14" s="57" t="s">
@@ -5309,7 +4559,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9"/>
       <c r="B15" s="123" t="s">
         <v>45</v>
@@ -5553,7 +4803,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9"/>
       <c r="B16" s="123"/>
       <c r="C16" s="57" t="s">
@@ -5795,7 +5045,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="10"/>
       <c r="B17" s="123" t="s">
         <v>46</v>
@@ -6039,7 +5289,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="10"/>
       <c r="B18" s="123"/>
       <c r="C18" s="57" t="s">
@@ -6281,7 +5531,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="9"/>
       <c r="B19" s="123" t="s">
         <v>47</v>
@@ -6525,7 +5775,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="9"/>
       <c r="B20" s="123"/>
       <c r="C20" s="57" t="s">
@@ -6767,7 +6017,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="9"/>
       <c r="B21" s="123" t="s">
         <v>48</v>
@@ -7011,7 +6261,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="9"/>
       <c r="B22" s="123"/>
       <c r="C22" s="57" t="s">
@@ -7253,7 +6503,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="9"/>
       <c r="B23" s="123" t="s">
         <v>49</v>
@@ -7489,7 +6739,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="9"/>
       <c r="B24" s="123"/>
       <c r="C24" s="57"/>
@@ -7723,7 +6973,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="9"/>
       <c r="B25" s="123" t="s">
         <v>50</v>
@@ -7959,7 +7209,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="9"/>
       <c r="B26" s="123"/>
       <c r="C26" s="57"/>
@@ -8193,7 +7443,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="9"/>
       <c r="B27" s="123" t="s">
         <v>51</v>
@@ -8429,7 +7679,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="9"/>
       <c r="B28" s="61"/>
       <c r="C28" s="57"/>
@@ -8663,7 +7913,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="9"/>
       <c r="B29" s="113"/>
       <c r="C29" s="57"/>
@@ -8897,7 +8147,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="9"/>
       <c r="B30" s="61"/>
       <c r="C30" s="57"/>
@@ -9131,7 +8381,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="9"/>
       <c r="B31" s="61"/>
       <c r="C31" s="57"/>
@@ -9365,7 +8615,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="9"/>
       <c r="B32" s="61"/>
       <c r="C32" s="57"/>
@@ -9599,7 +8849,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="9"/>
       <c r="B33" s="61"/>
       <c r="C33" s="57"/>
@@ -9833,7 +9083,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="9"/>
       <c r="B34" s="61"/>
       <c r="C34" s="57"/>
@@ -10067,7 +9317,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="9"/>
       <c r="B35" s="61"/>
       <c r="C35" s="57"/>
@@ -10302,7 +9552,7 @@
       </c>
       <c r="BM35" s="86"/>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="10"/>
       <c r="B36" s="115" t="s">
         <v>18</v>
@@ -10370,12 +9620,12 @@
       <c r="BK36" s="84"/>
       <c r="BL36" s="84"/>
     </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D37" s="4"/>
       <c r="G37" s="11"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D38" s="5"/>
     </row>
   </sheetData>
@@ -10404,39 +9654,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="81" priority="4">
+    <cfRule type="expression" dxfId="26" priority="4">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:BL6">
-    <cfRule type="expression" dxfId="80" priority="2">
+    <cfRule type="expression" dxfId="25" priority="2">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BL36">
-    <cfRule type="expression" dxfId="79" priority="1">
+    <cfRule type="expression" dxfId="24" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:BL35">
-    <cfRule type="expression" dxfId="78" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="7" stopIfTrue="1">
       <formula>AND($C10="Geringes Risiko",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="8" stopIfTrue="1">
       <formula>AND($C10="Hohes Risiko",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="9" stopIfTrue="1">
       <formula>AND($C10="Im Plan",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="10" stopIfTrue="1">
       <formula>AND($C10="Mittleres Risiko",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="11" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="73" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10535,44 +9785,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="9" max="64" width="3.5703125" customWidth="1"/>
-    <col min="65" max="65" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.73046875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="37.86328125" customWidth="1"/>
+    <col min="3" max="3" width="15.265625" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" customWidth="1"/>
+    <col min="5" max="5" width="15.73046875" customWidth="1"/>
+    <col min="6" max="6" width="10.3984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.3984375" customWidth="1"/>
+    <col min="8" max="8" width="2.73046875" customWidth="1"/>
+    <col min="9" max="64" width="3.59765625" customWidth="1"/>
+    <col min="65" max="65" width="2.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="10"/>
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="134"/>
-      <c r="L2" s="134"/>
-      <c r="M2" s="134"/>
-      <c r="N2" s="134"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="136"/>
-      <c r="S2" s="136"/>
-      <c r="T2" s="136"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="136"/>
+      <c r="P2" s="137"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
+      <c r="T2" s="137"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
       <c r="W2" s="20"/>
@@ -10619,7 +9869,7 @@
       <c r="BL2" s="20"/>
       <c r="BM2" s="20"/>
     </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="10"/>
       <c r="B3" s="40"/>
       <c r="C3" s="41"/>
@@ -10686,7 +9936,7 @@
       <c r="BL3" s="30"/>
       <c r="BM3" s="30"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="10"/>
       <c r="B4" s="52" t="s">
         <v>36</v>
@@ -10699,50 +9949,50 @@
         <v>30</v>
       </c>
       <c r="H4" s="27"/>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="131"/>
       <c r="O4" s="30"/>
-      <c r="P4" s="137" t="s">
+      <c r="P4" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137"/>
+      <c r="Q4" s="138"/>
+      <c r="R4" s="138"/>
+      <c r="S4" s="138"/>
+      <c r="T4" s="138"/>
+      <c r="U4" s="138"/>
       <c r="V4" s="30"/>
-      <c r="W4" s="138" t="s">
+      <c r="W4" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="138"/>
-      <c r="Z4" s="138"/>
-      <c r="AA4" s="138"/>
-      <c r="AB4" s="138"/>
+      <c r="X4" s="139"/>
+      <c r="Y4" s="139"/>
+      <c r="Z4" s="139"/>
+      <c r="AA4" s="139"/>
+      <c r="AB4" s="139"/>
       <c r="AC4" s="30"/>
-      <c r="AD4" s="139" t="s">
+      <c r="AD4" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="AE4" s="139"/>
-      <c r="AF4" s="139"/>
-      <c r="AG4" s="139"/>
-      <c r="AH4" s="139"/>
+      <c r="AE4" s="140"/>
+      <c r="AF4" s="140"/>
+      <c r="AG4" s="140"/>
+      <c r="AH4" s="140"/>
       <c r="AI4" s="30"/>
-      <c r="AJ4" s="132" t="s">
+      <c r="AJ4" s="133" t="s">
         <v>33</v>
       </c>
-      <c r="AK4" s="132"/>
-      <c r="AL4" s="132"/>
-      <c r="AM4" s="132"/>
-      <c r="AN4" s="132"/>
-      <c r="AO4" s="132"/>
-      <c r="AP4" s="132"/>
+      <c r="AK4" s="133"/>
+      <c r="AL4" s="133"/>
+      <c r="AM4" s="133"/>
+      <c r="AN4" s="133"/>
+      <c r="AO4" s="133"/>
+      <c r="AP4" s="133"/>
       <c r="AQ4" s="30"/>
       <c r="AR4" s="30"/>
       <c r="AS4" s="30"/>
@@ -10767,7 +10017,7 @@
       <c r="BL4" s="30"/>
       <c r="BM4" s="30"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
@@ -10838,7 +10088,7 @@
       <c r="BL5" s="30"/>
       <c r="BM5" s="30"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A6" s="10"/>
       <c r="B6" s="47" t="s">
         <v>6</v>
@@ -10933,7 +10183,7 @@
       <c r="BL6" s="63"/>
       <c r="BM6" s="30"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="10"/>
       <c r="B7" s="47" t="s">
         <v>7</v>
@@ -11172,7 +10422,7 @@
       </c>
       <c r="BM7" s="30"/>
     </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="10"/>
       <c r="B8" s="49"/>
       <c r="C8" s="49"/>
@@ -11239,7 +10489,7 @@
       <c r="BL8" s="37"/>
       <c r="BM8" s="30"/>
     </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
@@ -11488,7 +10738,7 @@
       </c>
       <c r="BM9" s="30"/>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="16"/>
       <c r="C10" s="13"/>
       <c r="D10" s="12"/>
@@ -11554,7 +10804,7 @@
       <c r="BL10" s="34"/>
       <c r="BM10" s="30"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="120" t="s">
         <v>38</v>
@@ -11795,7 +11045,7 @@
       </c>
       <c r="BP11" s="39"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="10"/>
       <c r="B12" s="121" t="s">
         <v>43</v>
@@ -12045,7 +11295,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="10"/>
       <c r="B13" s="121"/>
       <c r="C13" s="21" t="s">
@@ -12293,7 +11543,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="9"/>
       <c r="B14" s="121" t="s">
         <v>44</v>
@@ -12543,7 +11793,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9"/>
       <c r="B15" s="121"/>
       <c r="C15" s="21" t="s">
@@ -12791,7 +12041,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9"/>
       <c r="B16" s="121" t="s">
         <v>59</v>
@@ -13041,7 +12291,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="10"/>
       <c r="B17" s="121"/>
       <c r="C17" s="21" t="s">
@@ -13161,7 +12411,7 @@
         <v/>
       </c>
       <c r="AH17" s="45" t="str">
-        <f t="shared" ref="AH17:AW35" ca="1" si="7">IF(AND($C17="Ziel",AH$7&gt;=$F17,AH$7&lt;=$F17+$G17-1),2,IF(AND($C17="Meilenstein",AH$7&gt;=$F17,AH$7&lt;=$F17+$G17-1),1,""))</f>
+        <f t="shared" ref="AH17:AW32" ca="1" si="7">IF(AND($C17="Ziel",AH$7&gt;=$F17,AH$7&lt;=$F17+$G17-1),2,IF(AND($C17="Meilenstein",AH$7&gt;=$F17,AH$7&lt;=$F17+$G17-1),1,""))</f>
         <v/>
       </c>
       <c r="AI17" s="45" t="str">
@@ -13225,7 +12475,7 @@
         <v/>
       </c>
       <c r="AX17" s="45" t="str">
-        <f t="shared" ref="AX17:BM35" ca="1" si="8">IF(AND($C17="Ziel",AX$7&gt;=$F17,AX$7&lt;=$F17+$G17-1),2,IF(AND($C17="Meilenstein",AX$7&gt;=$F17,AX$7&lt;=$F17+$G17-1),1,""))</f>
+        <f t="shared" ref="AX17:BM32" ca="1" si="8">IF(AND($C17="Ziel",AX$7&gt;=$F17,AX$7&lt;=$F17+$G17-1),2,IF(AND($C17="Meilenstein",AX$7&gt;=$F17,AX$7&lt;=$F17+$G17-1),1,""))</f>
         <v/>
       </c>
       <c r="AY17" s="45" t="str">
@@ -13289,7 +12539,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="10"/>
       <c r="B18" s="121" t="s">
         <v>57</v>
@@ -13375,7 +12625,7 @@
         <v/>
       </c>
       <c r="Y18" s="45" t="str">
-        <f t="shared" ref="Y18:AN35" ca="1" si="9">IF(AND($C18="Ziel",Y$7&gt;=$F18,Y$7&lt;=$F18+$G18-1),2,IF(AND($C18="Meilenstein",Y$7&gt;=$F18,Y$7&lt;=$F18+$G18-1),1,""))</f>
+        <f t="shared" ref="Y18:AN32" ca="1" si="9">IF(AND($C18="Ziel",Y$7&gt;=$F18,Y$7&lt;=$F18+$G18-1),2,IF(AND($C18="Meilenstein",Y$7&gt;=$F18,Y$7&lt;=$F18+$G18-1),1,""))</f>
         <v/>
       </c>
       <c r="Z18" s="45" t="str">
@@ -13539,7 +12789,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="9"/>
       <c r="B19" s="12"/>
       <c r="C19" s="21" t="s">
@@ -13787,7 +13037,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="9"/>
       <c r="B20" s="121" t="s">
         <v>60</v>
@@ -14037,9 +13287,9 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="9"/>
-      <c r="B21" s="143"/>
+      <c r="B21" s="124"/>
       <c r="C21" s="21" t="s">
         <v>42</v>
       </c>
@@ -14285,15 +13535,17 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="9"/>
       <c r="B22" s="121" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="21"/>
+      <c r="D22" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="E22" s="22">
         <v>0</v>
       </c>
@@ -14301,7 +13553,7 @@
         <v>45993</v>
       </c>
       <c r="G22" s="24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="19"/>
       <c r="I22" s="45" t="str">
@@ -14533,20 +13785,24 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="9"/>
       <c r="B23" s="121"/>
       <c r="C23" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="21"/>
+      <c r="D23" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="E23" s="22">
         <v>0</v>
       </c>
       <c r="F23" s="23">
         <v>45993</v>
       </c>
-      <c r="G23" s="24"/>
+      <c r="G23" s="24">
+        <v>1</v>
+      </c>
       <c r="H23" s="19"/>
       <c r="I23" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14777,15 +14033,17 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="9"/>
       <c r="B24" s="121" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C24" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="21"/>
+      <c r="D24" s="21" t="s">
+        <v>53</v>
+      </c>
       <c r="E24" s="22">
         <v>0</v>
       </c>
@@ -15025,7 +14283,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="9"/>
       <c r="B25" s="121"/>
       <c r="C25" s="21" t="s">
@@ -15269,7 +14527,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="9"/>
       <c r="B26" s="121" t="s">
         <v>49</v>
@@ -15277,7 +14535,9 @@
       <c r="C26" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="21"/>
+      <c r="D26" s="21" t="s">
+        <v>66</v>
+      </c>
       <c r="E26" s="22">
         <v>0</v>
       </c>
@@ -15517,7 +14777,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="9"/>
       <c r="B27" s="121"/>
       <c r="C27" s="21" t="s">
@@ -15757,7 +15017,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="9"/>
       <c r="B28" s="121" t="s">
         <v>50</v>
@@ -15999,7 +15259,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="9"/>
       <c r="B29" s="121"/>
       <c r="C29" s="21" t="s">
@@ -16239,7 +15499,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="9"/>
       <c r="B30" s="121" t="s">
         <v>51</v>
@@ -16481,7 +15741,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="9"/>
       <c r="B31" s="121"/>
       <c r="C31" s="21" t="s">
@@ -16721,7 +15981,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="9"/>
       <c r="B32" s="121"/>
       <c r="C32" s="21" t="s">
@@ -16961,7 +16221,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="9"/>
       <c r="B33" s="121"/>
       <c r="C33" s="21" t="s">
@@ -17201,7 +16461,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="9"/>
       <c r="B34" s="121"/>
       <c r="C34" s="21" t="s">
@@ -17441,7 +16701,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="9"/>
       <c r="B35" s="121"/>
       <c r="C35" s="21" t="s">
@@ -17681,7 +16941,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="10"/>
       <c r="B36" s="114" t="s">
         <v>18</v>
@@ -17750,12 +17010,12 @@
       <c r="BL36" s="54"/>
       <c r="BM36" s="26"/>
     </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D37" s="4"/>
       <c r="G37" s="11"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D38" s="5"/>
     </row>
   </sheetData>
@@ -17785,39 +17045,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="72" priority="4">
+    <cfRule type="expression" dxfId="17" priority="4">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:BL6">
-    <cfRule type="expression" dxfId="71" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:BL10 I36:BL36 I11:BM35">
+  <conditionalFormatting sqref="I7:BL10 I11:BM35 I36:BL36">
     <cfRule type="expression" dxfId="15" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:BL10 I11:BM35">
-    <cfRule type="expression" dxfId="70" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="7" stopIfTrue="1">
       <formula>AND($C10="Ist",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="8" stopIfTrue="1">
       <formula>AND($C10="Hohes Risiko",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="9" stopIfTrue="1">
       <formula>AND($C10="Soll",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="10" stopIfTrue="1">
       <formula>AND($C10="Mittleres Risiko",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="11" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="55" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17919,44 +17179,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="9" max="64" width="3.5703125" customWidth="1"/>
-    <col min="65" max="65" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.73046875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="37.86328125" customWidth="1"/>
+    <col min="3" max="3" width="15.265625" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" customWidth="1"/>
+    <col min="5" max="5" width="15.73046875" customWidth="1"/>
+    <col min="6" max="6" width="10.3984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.3984375" customWidth="1"/>
+    <col min="8" max="8" width="2.73046875" customWidth="1"/>
+    <col min="9" max="64" width="3.59765625" customWidth="1"/>
+    <col min="65" max="65" width="2.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="10"/>
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="141" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="140"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="142"/>
-      <c r="P2" s="142"/>
-      <c r="Q2" s="142"/>
-      <c r="R2" s="142"/>
-      <c r="S2" s="142"/>
-      <c r="T2" s="142"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="142"/>
+      <c r="M2" s="142"/>
+      <c r="N2" s="142"/>
+      <c r="O2" s="143"/>
+      <c r="P2" s="143"/>
+      <c r="Q2" s="143"/>
+      <c r="R2" s="143"/>
+      <c r="S2" s="143"/>
+      <c r="T2" s="143"/>
       <c r="U2" s="94"/>
       <c r="V2" s="94"/>
       <c r="W2" s="94"/>
@@ -18003,7 +17263,7 @@
       <c r="BL2" s="94"/>
       <c r="BM2" s="94"/>
     </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="10"/>
       <c r="B3" s="65"/>
       <c r="C3" s="66"/>
@@ -18017,7 +17277,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="10"/>
       <c r="B4" s="69" t="s">
         <v>4</v>
@@ -18030,48 +17290,48 @@
         <v>30</v>
       </c>
       <c r="H4" s="72"/>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="P4" s="137" t="s">
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="131"/>
+      <c r="P4" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="Q4" s="138"/>
+      <c r="R4" s="138"/>
+      <c r="S4" s="138"/>
+      <c r="T4" s="138"/>
+      <c r="U4" s="138"/>
+      <c r="W4" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="138"/>
-      <c r="Z4" s="138"/>
-      <c r="AA4" s="138"/>
-      <c r="AB4" s="138"/>
-      <c r="AD4" s="139" t="s">
+      <c r="X4" s="139"/>
+      <c r="Y4" s="139"/>
+      <c r="Z4" s="139"/>
+      <c r="AA4" s="139"/>
+      <c r="AB4" s="139"/>
+      <c r="AD4" s="140" t="s">
         <v>32</v>
       </c>
-      <c r="AE4" s="139"/>
-      <c r="AF4" s="139"/>
-      <c r="AG4" s="139"/>
-      <c r="AH4" s="139"/>
-      <c r="AJ4" s="132" t="s">
+      <c r="AE4" s="140"/>
+      <c r="AF4" s="140"/>
+      <c r="AG4" s="140"/>
+      <c r="AH4" s="140"/>
+      <c r="AJ4" s="133" t="s">
         <v>33</v>
       </c>
-      <c r="AK4" s="132"/>
-      <c r="AL4" s="132"/>
-      <c r="AM4" s="132"/>
-      <c r="AN4" s="132"/>
-      <c r="AO4" s="132"/>
-      <c r="AP4" s="132"/>
+      <c r="AK4" s="133"/>
+      <c r="AL4" s="133"/>
+      <c r="AM4" s="133"/>
+      <c r="AN4" s="133"/>
+      <c r="AO4" s="133"/>
+      <c r="AP4" s="133"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
@@ -18085,14 +17345,14 @@
       <c r="G5" s="72"/>
       <c r="H5" s="72"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A6" s="10"/>
       <c r="B6" s="76" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="77" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Meilensteine43524[Start])=0,TODAY(),B11(Meilensteine43524[Start])),TODAY())</f>
-        <v>45986</v>
+        <v>46007</v>
       </c>
       <c r="D6" s="78"/>
       <c r="E6" s="72"/>
@@ -18101,7 +17361,7 @@
       <c r="H6" s="72"/>
       <c r="I6" s="88" t="str">
         <f ca="1">TEXT(I7,"MMMM")</f>
-        <v>November</v>
+        <v>Dezember</v>
       </c>
       <c r="J6" s="88"/>
       <c r="K6" s="88"/>
@@ -18111,7 +17371,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="88" t="str">
         <f ca="1">IF(TEXT(P7,"MMMM")=I6,"",TEXT(P7,"MMMM"))</f>
-        <v>Dezember</v>
+        <v/>
       </c>
       <c r="Q6" s="88"/>
       <c r="R6" s="88"/>
@@ -18131,7 +17391,7 @@
       <c r="AC6" s="88"/>
       <c r="AD6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(AD7,"MMMM")=W6,TEXT(AD7,"MMMM")=P6,TEXT(AD7,"MMMM")=I6),"",TEXT(AD7,"MMMM"))</f>
-        <v/>
+        <v>Januar</v>
       </c>
       <c r="AE6" s="88"/>
       <c r="AF6" s="88"/>
@@ -18161,7 +17421,7 @@
       <c r="AX6" s="89"/>
       <c r="AY6" s="89" t="str">
         <f ca="1">IF(OR(TEXT(AY7,"MMMM")=AR6,TEXT(AY7,"MMMM")=AK6,TEXT(AY7,"MMMM")=AD6,TEXT(AY7,"MMMM")=W6),"",TEXT(AY7,"MMMM"))</f>
-        <v>Januar</v>
+        <v/>
       </c>
       <c r="AZ6" s="89"/>
       <c r="BA6" s="89"/>
@@ -18171,7 +17431,7 @@
       <c r="BE6" s="87"/>
       <c r="BF6" s="87" t="str">
         <f ca="1">IF(OR(TEXT(BF7,"MMMM")=AY6,TEXT(BF7,"MMMM")=AR6,TEXT(BF7,"MMMM")=AK6,TEXT(BF7,"MMMM")=AD6),"",TEXT(BF7,"MMMM"))</f>
-        <v/>
+        <v>Februar</v>
       </c>
       <c r="BG6" s="87"/>
       <c r="BH6" s="87"/>
@@ -18180,7 +17440,7 @@
       <c r="BK6" s="87"/>
       <c r="BL6" s="87"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="10"/>
       <c r="B7" s="76" t="s">
         <v>7</v>
@@ -18195,230 +17455,230 @@
       <c r="H7" s="80"/>
       <c r="I7" s="95">
         <f ca="1">IFERROR(Projekt_Start+Scrollschrittweite,TODAY())</f>
-        <v>45987</v>
+        <v>46008</v>
       </c>
       <c r="J7" s="96">
         <f ca="1">I7+1</f>
-        <v>45988</v>
+        <v>46009</v>
       </c>
       <c r="K7" s="96">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>45989</v>
+        <v>46010</v>
       </c>
       <c r="L7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>45990</v>
+        <v>46011</v>
       </c>
       <c r="M7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>45991</v>
+        <v>46012</v>
       </c>
       <c r="N7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>45992</v>
+        <v>46013</v>
       </c>
       <c r="O7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>45993</v>
+        <v>46014</v>
       </c>
       <c r="P7" s="96">
         <f ca="1">O7+1</f>
-        <v>45994</v>
+        <v>46015</v>
       </c>
       <c r="Q7" s="96">
         <f ca="1">P7+1</f>
-        <v>45995</v>
+        <v>46016</v>
       </c>
       <c r="R7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>45996</v>
+        <v>46017</v>
       </c>
       <c r="S7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>45997</v>
+        <v>46018</v>
       </c>
       <c r="T7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>45998</v>
+        <v>46019</v>
       </c>
       <c r="U7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>45999</v>
+        <v>46020</v>
       </c>
       <c r="V7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46000</v>
+        <v>46021</v>
       </c>
       <c r="W7" s="96">
         <f ca="1">V7+1</f>
-        <v>46001</v>
+        <v>46022</v>
       </c>
       <c r="X7" s="96">
         <f ca="1">W7+1</f>
-        <v>46002</v>
+        <v>46023</v>
       </c>
       <c r="Y7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46003</v>
+        <v>46024</v>
       </c>
       <c r="Z7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46004</v>
+        <v>46025</v>
       </c>
       <c r="AA7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46005</v>
+        <v>46026</v>
       </c>
       <c r="AB7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46006</v>
+        <v>46027</v>
       </c>
       <c r="AC7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46007</v>
+        <v>46028</v>
       </c>
       <c r="AD7" s="96">
         <f ca="1">AC7+1</f>
-        <v>46008</v>
+        <v>46029</v>
       </c>
       <c r="AE7" s="96">
         <f ca="1">AD7+1</f>
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="AF7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46010</v>
+        <v>46031</v>
       </c>
       <c r="AG7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46011</v>
+        <v>46032</v>
       </c>
       <c r="AH7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46012</v>
+        <v>46033</v>
       </c>
       <c r="AI7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46013</v>
+        <v>46034</v>
       </c>
       <c r="AJ7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46014</v>
+        <v>46035</v>
       </c>
       <c r="AK7" s="96">
         <f ca="1">AJ7+1</f>
-        <v>46015</v>
+        <v>46036</v>
       </c>
       <c r="AL7" s="96">
         <f ca="1">AK7+1</f>
-        <v>46016</v>
+        <v>46037</v>
       </c>
       <c r="AM7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46017</v>
+        <v>46038</v>
       </c>
       <c r="AN7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46018</v>
+        <v>46039</v>
       </c>
       <c r="AO7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46019</v>
+        <v>46040</v>
       </c>
       <c r="AP7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46020</v>
+        <v>46041</v>
       </c>
       <c r="AQ7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46021</v>
+        <v>46042</v>
       </c>
       <c r="AR7" s="96">
         <f ca="1">AQ7+1</f>
-        <v>46022</v>
+        <v>46043</v>
       </c>
       <c r="AS7" s="96">
         <f ca="1">AR7+1</f>
-        <v>46023</v>
+        <v>46044</v>
       </c>
       <c r="AT7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46024</v>
+        <v>46045</v>
       </c>
       <c r="AU7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46025</v>
+        <v>46046</v>
       </c>
       <c r="AV7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46026</v>
+        <v>46047</v>
       </c>
       <c r="AW7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46027</v>
+        <v>46048</v>
       </c>
       <c r="AX7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46028</v>
+        <v>46049</v>
       </c>
       <c r="AY7" s="96">
         <f ca="1">AX7+1</f>
-        <v>46029</v>
+        <v>46050</v>
       </c>
       <c r="AZ7" s="96">
         <f ca="1">AY7+1</f>
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="BA7" s="96">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46031</v>
+        <v>46052</v>
       </c>
       <c r="BB7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46032</v>
+        <v>46053</v>
       </c>
       <c r="BC7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46033</v>
+        <v>46054</v>
       </c>
       <c r="BD7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46034</v>
+        <v>46055</v>
       </c>
       <c r="BE7" s="97">
         <f t="shared" ca="1" si="1"/>
-        <v>46035</v>
+        <v>46056</v>
       </c>
       <c r="BF7" s="96">
         <f ca="1">BE7+1</f>
-        <v>46036</v>
+        <v>46057</v>
       </c>
       <c r="BG7" s="96">
         <f ca="1">BF7+1</f>
-        <v>46037</v>
+        <v>46058</v>
       </c>
       <c r="BH7" s="96">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46038</v>
+        <v>46059</v>
       </c>
       <c r="BI7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46039</v>
+        <v>46060</v>
       </c>
       <c r="BJ7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46040</v>
+        <v>46061</v>
       </c>
       <c r="BK7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46041</v>
+        <v>46062</v>
       </c>
       <c r="BL7" s="97">
         <f t="shared" ca="1" si="2"/>
-        <v>46042</v>
+        <v>46063</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="10"/>
       <c r="B8" s="71"/>
       <c r="C8" s="71"/>
@@ -18484,7 +17744,7 @@
       <c r="BK8" s="99"/>
       <c r="BL8" s="102"/>
     </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
@@ -18732,7 +17992,7 @@
         <v>D</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="16"/>
       <c r="C10" s="13"/>
       <c r="D10" s="12"/>
@@ -18796,7 +18056,7 @@
       <c r="BK10" s="34"/>
       <c r="BL10" s="34"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="10"/>
       <c r="B11" s="113" t="s">
         <v>9</v>
@@ -19033,7 +18293,7 @@
       </c>
       <c r="BP11" s="39"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="10"/>
       <c r="B12" s="61" t="s">
         <v>10</v>
@@ -19049,7 +18309,7 @@
       </c>
       <c r="F12" s="59">
         <f ca="1">TODAY()</f>
-        <v>45986</v>
+        <v>46007</v>
       </c>
       <c r="G12" s="60">
         <v>3</v>
@@ -19280,7 +18540,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="10"/>
       <c r="B13" s="61" t="s">
         <v>11</v>
@@ -19292,7 +18552,7 @@
       <c r="E13" s="58"/>
       <c r="F13" s="59">
         <f ca="1">TODAY()+5</f>
-        <v>45991</v>
+        <v>46012</v>
       </c>
       <c r="G13" s="60">
         <v>1</v>
@@ -19523,7 +18783,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="9"/>
       <c r="B14" s="61" t="s">
         <v>12</v>
@@ -19537,7 +18797,7 @@
       </c>
       <c r="F14" s="59">
         <f ca="1">F12-3</f>
-        <v>45983</v>
+        <v>46004</v>
       </c>
       <c r="G14" s="60">
         <v>10</v>
@@ -19768,7 +19028,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9"/>
       <c r="B15" s="61" t="s">
         <v>13</v>
@@ -19780,7 +19040,7 @@
       <c r="E15" s="58"/>
       <c r="F15" s="59">
         <f ca="1">F12+20</f>
-        <v>46006</v>
+        <v>46027</v>
       </c>
       <c r="G15" s="60">
         <v>1</v>
@@ -20011,7 +19271,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9"/>
       <c r="B16" s="61" t="s">
         <v>14</v>
@@ -20025,7 +19285,7 @@
       </c>
       <c r="F16" s="59">
         <f ca="1">F12+6</f>
-        <v>45992</v>
+        <v>46013</v>
       </c>
       <c r="G16" s="60">
         <v>6</v>
@@ -20256,7 +19516,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="10"/>
       <c r="B17" s="113" t="s">
         <v>15</v>
@@ -20492,7 +19752,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="10"/>
       <c r="B18" s="61" t="s">
         <v>10</v>
@@ -20506,7 +19766,7 @@
       </c>
       <c r="F18" s="59">
         <f ca="1">F12+6</f>
-        <v>45992</v>
+        <v>46013</v>
       </c>
       <c r="G18" s="60">
         <v>13</v>
@@ -20737,7 +19997,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="9"/>
       <c r="B19" s="61" t="s">
         <v>11</v>
@@ -20751,7 +20011,7 @@
       </c>
       <c r="F19" s="59">
         <f ca="1">F18+2</f>
-        <v>45994</v>
+        <v>46015</v>
       </c>
       <c r="G19" s="60">
         <v>9</v>
@@ -20982,7 +20242,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="9"/>
       <c r="B20" s="61" t="s">
         <v>12</v>
@@ -20996,7 +20256,7 @@
       </c>
       <c r="F20" s="59">
         <f ca="1">F19+5</f>
-        <v>45999</v>
+        <v>46020</v>
       </c>
       <c r="G20" s="60">
         <v>11</v>
@@ -21227,7 +20487,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="9"/>
       <c r="B21" s="61" t="s">
         <v>13</v>
@@ -21239,7 +20499,7 @@
       <c r="E21" s="58"/>
       <c r="F21" s="59">
         <f ca="1">F20+2</f>
-        <v>46001</v>
+        <v>46022</v>
       </c>
       <c r="G21" s="60">
         <v>1</v>
@@ -21470,7 +20730,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="9"/>
       <c r="B22" s="61" t="s">
         <v>14</v>
@@ -21480,7 +20740,7 @@
       <c r="E22" s="58"/>
       <c r="F22" s="59">
         <f ca="1">F21+1</f>
-        <v>46002</v>
+        <v>46023</v>
       </c>
       <c r="G22" s="60">
         <v>24</v>
@@ -21711,7 +20971,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="9"/>
       <c r="B23" s="113" t="s">
         <v>16</v>
@@ -21947,7 +21207,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="9"/>
       <c r="B24" s="61" t="s">
         <v>10</v>
@@ -21959,7 +21219,7 @@
       <c r="E24" s="58"/>
       <c r="F24" s="59">
         <f ca="1">F12+15</f>
-        <v>46001</v>
+        <v>46022</v>
       </c>
       <c r="G24" s="60">
         <v>4</v>
@@ -22190,7 +21450,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="9"/>
       <c r="B25" s="61" t="s">
         <v>11</v>
@@ -22202,7 +21462,7 @@
       <c r="E25" s="58"/>
       <c r="F25" s="59">
         <f ca="1">F24+3</f>
-        <v>46004</v>
+        <v>46025</v>
       </c>
       <c r="G25" s="60">
         <v>14</v>
@@ -22433,7 +21693,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="9"/>
       <c r="B26" s="61" t="s">
         <v>12</v>
@@ -22445,7 +21705,7 @@
       <c r="E26" s="58"/>
       <c r="F26" s="59">
         <f ca="1">F25+15</f>
-        <v>46019</v>
+        <v>46040</v>
       </c>
       <c r="G26" s="60">
         <v>6</v>
@@ -22676,7 +21936,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="9"/>
       <c r="B27" s="61" t="s">
         <v>13</v>
@@ -22688,7 +21948,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="59">
         <f ca="1">F21+22</f>
-        <v>46023</v>
+        <v>46044</v>
       </c>
       <c r="G27" s="60">
         <v>3</v>
@@ -22919,7 +22179,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="9"/>
       <c r="B28" s="61" t="s">
         <v>14</v>
@@ -22931,7 +22191,7 @@
       <c r="E28" s="58"/>
       <c r="F28" s="59">
         <f ca="1">F16</f>
-        <v>45992</v>
+        <v>46013</v>
       </c>
       <c r="G28" s="60">
         <v>19</v>
@@ -23162,7 +22422,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="9"/>
       <c r="B29" s="113" t="s">
         <v>17</v>
@@ -23398,7 +22658,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="9"/>
       <c r="B30" s="61" t="s">
         <v>10</v>
@@ -23408,7 +22668,7 @@
       <c r="E30" s="58"/>
       <c r="F30" s="59">
         <f ca="1">F27+3</f>
-        <v>46026</v>
+        <v>46047</v>
       </c>
       <c r="G30" s="60">
         <v>15</v>
@@ -23639,7 +22899,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="9"/>
       <c r="B31" s="61" t="s">
         <v>11</v>
@@ -23649,7 +22909,7 @@
       <c r="E31" s="58"/>
       <c r="F31" s="59">
         <f ca="1">F30+14</f>
-        <v>46040</v>
+        <v>46061</v>
       </c>
       <c r="G31" s="60">
         <v>5</v>
@@ -23880,7 +23140,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="9"/>
       <c r="B32" s="61" t="s">
         <v>12</v>
@@ -23892,7 +23152,7 @@
       <c r="E32" s="58"/>
       <c r="F32" s="59">
         <f ca="1">F31+42</f>
-        <v>46082</v>
+        <v>46103</v>
       </c>
       <c r="G32" s="60">
         <v>1</v>
@@ -24123,7 +23383,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="9"/>
       <c r="B33" s="61" t="s">
         <v>13</v>
@@ -24359,7 +23619,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="9"/>
       <c r="B34" s="61" t="s">
         <v>14</v>
@@ -24595,7 +23855,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="9"/>
       <c r="B35" s="61"/>
       <c r="C35" s="57"/>
@@ -24830,7 +24090,7 @@
       </c>
       <c r="BM35" s="86"/>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="10"/>
       <c r="B36" s="115" t="s">
         <v>18</v>
@@ -24898,12 +24158,12 @@
       <c r="BK36" s="84"/>
       <c r="BL36" s="84"/>
     </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D37" s="4"/>
       <c r="G37" s="11"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="D38" s="5"/>
     </row>
   </sheetData>
@@ -24932,39 +24192,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="24" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:BL6">
-    <cfRule type="expression" dxfId="23" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BL36">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:BL35">
-    <cfRule type="expression" dxfId="21" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>AND($C10="Geringes Risiko",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>AND($C10="Hohes Risiko",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="9" stopIfTrue="1">
       <formula>AND($C10="Im Plan",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="10" stopIfTrue="1">
       <formula>AND($C10="Mittleres Risiko",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="11" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25355,15 +24615,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -25381,6 +24632,15 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25405,14 +24665,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAF2F40C-D12E-4644-AA6E-31E499F048DC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CD6AD73-D703-40CF-AB8D-72E6A3921BEB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -25422,4 +24674,12 @@
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAF2F40C-D12E-4644-AA6E-31E499F048DC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Diagramme/SmartClock_Gantt-Diagramm_V2.xlsx
+++ b/Diagramme/SmartClock_Gantt-Diagramm_V2.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="664" documentId="8_{0C4EAEB1-A5C4-4402-980F-B32D81185735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98B27C84-C4C2-4BB9-B97A-BDE1A1E0F90D}"/>
+  <xr:revisionPtr revIDLastSave="684" documentId="8_{0C4EAEB1-A5C4-4402-980F-B32D81185735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE44A00B-A8B7-455F-BA14-85B51F32F1F8}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" tabRatio="415" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1665" windowWidth="29040" windowHeight="15720" tabRatio="415" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="12" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="58">
   <si>
     <t>INFORMATIONEN ZU DIESEM GANTT-DIAGRAMM</t>
   </si>
@@ -235,46 +235,19 @@
     <t>Aufwand Soll / Ist</t>
   </si>
   <si>
-    <t>14h</t>
+    <t>Timer einstellen</t>
   </si>
   <si>
-    <t>5h</t>
+    <t>Timer starten (können)</t>
   </si>
   <si>
-    <t>4.5h</t>
+    <t>Timer läuft (Anzeige)</t>
   </si>
   <si>
-    <t>16h</t>
+    <t>Timer buzzed</t>
   </si>
   <si>
-    <t>Project documentation</t>
-  </si>
-  <si>
-    <t>12h</t>
-  </si>
-  <si>
-    <t>Planning solder joystick</t>
-  </si>
-  <si>
-    <t>Flowchart timer function</t>
-  </si>
-  <si>
-    <t>4h</t>
-  </si>
-  <si>
-    <t>6h</t>
-  </si>
-  <si>
-    <t>2h</t>
-  </si>
-  <si>
-    <t>Joystick gestures</t>
-  </si>
-  <si>
-    <t>Set Timer using Joystick</t>
-  </si>
-  <si>
-    <t>7h</t>
+    <t>Code Optimierung</t>
   </si>
 </sst>
 </file>
@@ -861,7 +834,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1195,9 +1168,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="13" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2549,26 +2519,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="13.15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.73046875" style="8" customWidth="1"/>
-    <col min="2" max="2" width="2.73046875" style="8" customWidth="1"/>
-    <col min="3" max="5" width="40.73046875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="9.1328125" style="6"/>
+    <col min="1" max="1" width="4.7109375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" style="8" customWidth="1"/>
+    <col min="3" max="5" width="40.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" style="6" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" ht="28.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:13" s="7" customFormat="1" ht="28.5" x14ac:dyDescent="0.4">
       <c r="D1" s="104"/>
     </row>
-    <row r="2" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7"/>
       <c r="B2" s="110"/>
-      <c r="C2" s="125" t="s">
+      <c r="C2" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
       <c r="F2" s="110"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -2578,7 +2548,7 @@
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
     </row>
-    <row r="3" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
       <c r="B3" s="105"/>
       <c r="C3" s="106"/>
@@ -2593,14 +2563,14 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
       <c r="B4" s="105"/>
-      <c r="C4" s="126" t="s">
+      <c r="C4" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="125"/>
       <c r="F4" s="105"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -2610,14 +2580,14 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="7"/>
       <c r="B5" s="105"/>
-      <c r="C5" s="126" t="s">
+      <c r="C5" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
       <c r="F5" s="105"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -2627,7 +2597,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" ht="14.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="108"/>
       <c r="C6" s="108"/>
@@ -2635,15 +2605,15 @@
       <c r="E6" s="108"/>
       <c r="F6" s="108"/>
     </row>
-    <row r="7" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
     </row>
-    <row r="8" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
     </row>
-    <row r="9" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -2651,51 +2621,51 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="D18" s="8"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="D19" s="8"/>
@@ -2718,44 +2688,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.73046875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.86328125" customWidth="1"/>
-    <col min="3" max="3" width="15.265625" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" customWidth="1"/>
-    <col min="5" max="5" width="15.73046875" customWidth="1"/>
-    <col min="6" max="6" width="10.3984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" customWidth="1"/>
-    <col min="8" max="8" width="2.73046875" customWidth="1"/>
-    <col min="9" max="64" width="3.59765625" customWidth="1"/>
-    <col min="65" max="65" width="2.73046875" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" customWidth="1"/>
+    <col min="9" max="64" width="3.5703125" customWidth="1"/>
+    <col min="65" max="65" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
-      <c r="B2" s="128" t="s">
+      <c r="B2" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="130"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="130"/>
-      <c r="S2" s="130"/>
-      <c r="T2" s="130"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="127"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
       <c r="U2" s="64"/>
       <c r="V2" s="64"/>
       <c r="W2" s="64"/>
@@ -2802,7 +2772,7 @@
       <c r="BL2" s="64"/>
       <c r="BM2" s="64"/>
     </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="65"/>
       <c r="C3" s="66"/>
@@ -2816,7 +2786,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="69" t="s">
         <v>36</v>
@@ -2829,40 +2799,40 @@
         <v>30</v>
       </c>
       <c r="H4" s="72"/>
-      <c r="I4" s="131" t="s">
+      <c r="I4" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="132"/>
-      <c r="R4" s="132"/>
-      <c r="S4" s="132"/>
-      <c r="T4" s="132"/>
-      <c r="U4" s="132"/>
-      <c r="W4" s="132"/>
-      <c r="X4" s="132"/>
-      <c r="Y4" s="132"/>
-      <c r="Z4" s="132"/>
-      <c r="AA4" s="132"/>
-      <c r="AB4" s="132"/>
-      <c r="AD4" s="132"/>
-      <c r="AE4" s="132"/>
-      <c r="AF4" s="132"/>
-      <c r="AG4" s="132"/>
-      <c r="AH4" s="132"/>
-      <c r="AJ4" s="127"/>
-      <c r="AK4" s="127"/>
-      <c r="AL4" s="127"/>
-      <c r="AM4" s="127"/>
-      <c r="AN4" s="127"/>
-      <c r="AO4" s="127"/>
-      <c r="AP4" s="127"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="131"/>
+      <c r="T4" s="131"/>
+      <c r="U4" s="131"/>
+      <c r="W4" s="131"/>
+      <c r="X4" s="131"/>
+      <c r="Y4" s="131"/>
+      <c r="Z4" s="131"/>
+      <c r="AA4" s="131"/>
+      <c r="AB4" s="131"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="131"/>
+      <c r="AF4" s="131"/>
+      <c r="AG4" s="131"/>
+      <c r="AH4" s="131"/>
+      <c r="AJ4" s="126"/>
+      <c r="AK4" s="126"/>
+      <c r="AL4" s="126"/>
+      <c r="AM4" s="126"/>
+      <c r="AN4" s="126"/>
+      <c r="AO4" s="126"/>
+      <c r="AP4" s="126"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
@@ -2876,7 +2846,7 @@
       <c r="G5" s="72"/>
       <c r="H5" s="72"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="76" t="s">
         <v>6</v>
@@ -2970,7 +2940,7 @@
       <c r="BK6" s="87"/>
       <c r="BL6" s="87"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="76" t="s">
         <v>7</v>
@@ -3208,7 +3178,7 @@
         <v>46021</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="71"/>
       <c r="C8" s="71"/>
@@ -3274,7 +3244,7 @@
       <c r="BK8" s="99"/>
       <c r="BL8" s="102"/>
     </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
@@ -3522,7 +3492,7 @@
         <v>D</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="16"/>
       <c r="C10" s="13"/>
       <c r="D10" s="12"/>
@@ -3586,7 +3556,7 @@
       <c r="BK10" s="34"/>
       <c r="BL10" s="34"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="123" t="s">
         <v>43</v>
@@ -3831,7 +3801,7 @@
       </c>
       <c r="BP11" s="39"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="123"/>
       <c r="C12" s="57" t="s">
@@ -4073,7 +4043,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="123" t="s">
         <v>44</v>
@@ -4317,7 +4287,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="123"/>
       <c r="C14" s="57" t="s">
@@ -4559,7 +4529,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="123" t="s">
         <v>45</v>
@@ -4803,7 +4773,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="123"/>
       <c r="C16" s="57" t="s">
@@ -5045,7 +5015,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="123" t="s">
         <v>46</v>
@@ -5289,7 +5259,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="123"/>
       <c r="C18" s="57" t="s">
@@ -5531,7 +5501,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="B19" s="123" t="s">
         <v>47</v>
@@ -5775,7 +5745,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="123"/>
       <c r="C20" s="57" t="s">
@@ -6017,7 +5987,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="123" t="s">
         <v>48</v>
@@ -6261,7 +6231,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="123"/>
       <c r="C22" s="57" t="s">
@@ -6503,7 +6473,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="123" t="s">
         <v>49</v>
@@ -6739,7 +6709,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
       <c r="B24" s="123"/>
       <c r="C24" s="57"/>
@@ -6973,7 +6943,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="123" t="s">
         <v>50</v>
@@ -7209,7 +7179,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="B26" s="123"/>
       <c r="C26" s="57"/>
@@ -7443,7 +7413,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="123" t="s">
         <v>51</v>
@@ -7679,7 +7649,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
       <c r="B28" s="61"/>
       <c r="C28" s="57"/>
@@ -7913,7 +7883,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
       <c r="B29" s="113"/>
       <c r="C29" s="57"/>
@@ -8147,7 +8117,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
       <c r="B30" s="61"/>
       <c r="C30" s="57"/>
@@ -8381,7 +8351,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
       <c r="B31" s="61"/>
       <c r="C31" s="57"/>
@@ -8615,7 +8585,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="61"/>
       <c r="C32" s="57"/>
@@ -8849,7 +8819,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="61"/>
       <c r="C33" s="57"/>
@@ -9083,7 +9053,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
       <c r="B34" s="61"/>
       <c r="C34" s="57"/>
@@ -9317,7 +9287,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
       <c r="B35" s="61"/>
       <c r="C35" s="57"/>
@@ -9552,7 +9522,7 @@
       </c>
       <c r="BM35" s="86"/>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="115" t="s">
         <v>18</v>
@@ -9620,12 +9590,12 @@
       <c r="BK36" s="84"/>
       <c r="BL36" s="84"/>
     </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="4"/>
       <c r="G37" s="11"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="5"/>
     </row>
   </sheetData>
@@ -9785,44 +9755,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.73046875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.86328125" customWidth="1"/>
-    <col min="3" max="3" width="15.265625" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" customWidth="1"/>
-    <col min="5" max="5" width="15.73046875" customWidth="1"/>
-    <col min="6" max="6" width="10.3984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" customWidth="1"/>
-    <col min="8" max="8" width="2.73046875" customWidth="1"/>
-    <col min="9" max="64" width="3.59765625" customWidth="1"/>
-    <col min="65" max="65" width="2.73046875" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" customWidth="1"/>
+    <col min="9" max="64" width="3.5703125" customWidth="1"/>
+    <col min="65" max="65" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="133" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="135"/>
-      <c r="N2" s="135"/>
-      <c r="O2" s="136"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="134"/>
+      <c r="L2" s="134"/>
+      <c r="M2" s="134"/>
+      <c r="N2" s="134"/>
+      <c r="O2" s="135"/>
+      <c r="P2" s="136"/>
+      <c r="Q2" s="136"/>
+      <c r="R2" s="136"/>
+      <c r="S2" s="136"/>
+      <c r="T2" s="136"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
       <c r="W2" s="20"/>
@@ -9869,7 +9839,7 @@
       <c r="BL2" s="20"/>
       <c r="BM2" s="20"/>
     </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="40"/>
       <c r="C3" s="41"/>
@@ -9936,7 +9906,7 @@
       <c r="BL3" s="30"/>
       <c r="BM3" s="30"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="52" t="s">
         <v>36</v>
@@ -9949,50 +9919,50 @@
         <v>30</v>
       </c>
       <c r="H4" s="27"/>
-      <c r="I4" s="131" t="s">
+      <c r="I4" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
       <c r="O4" s="30"/>
-      <c r="P4" s="138" t="s">
+      <c r="P4" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="138"/>
-      <c r="R4" s="138"/>
-      <c r="S4" s="138"/>
-      <c r="T4" s="138"/>
-      <c r="U4" s="138"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
       <c r="V4" s="30"/>
-      <c r="W4" s="139" t="s">
+      <c r="W4" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="X4" s="139"/>
-      <c r="Y4" s="139"/>
-      <c r="Z4" s="139"/>
-      <c r="AA4" s="139"/>
-      <c r="AB4" s="139"/>
+      <c r="X4" s="138"/>
+      <c r="Y4" s="138"/>
+      <c r="Z4" s="138"/>
+      <c r="AA4" s="138"/>
+      <c r="AB4" s="138"/>
       <c r="AC4" s="30"/>
-      <c r="AD4" s="140" t="s">
+      <c r="AD4" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="AE4" s="140"/>
-      <c r="AF4" s="140"/>
-      <c r="AG4" s="140"/>
-      <c r="AH4" s="140"/>
+      <c r="AE4" s="139"/>
+      <c r="AF4" s="139"/>
+      <c r="AG4" s="139"/>
+      <c r="AH4" s="139"/>
       <c r="AI4" s="30"/>
-      <c r="AJ4" s="133" t="s">
+      <c r="AJ4" s="132" t="s">
         <v>33</v>
       </c>
-      <c r="AK4" s="133"/>
-      <c r="AL4" s="133"/>
-      <c r="AM4" s="133"/>
-      <c r="AN4" s="133"/>
-      <c r="AO4" s="133"/>
-      <c r="AP4" s="133"/>
+      <c r="AK4" s="132"/>
+      <c r="AL4" s="132"/>
+      <c r="AM4" s="132"/>
+      <c r="AN4" s="132"/>
+      <c r="AO4" s="132"/>
+      <c r="AP4" s="132"/>
       <c r="AQ4" s="30"/>
       <c r="AR4" s="30"/>
       <c r="AS4" s="30"/>
@@ -10017,7 +9987,7 @@
       <c r="BL4" s="30"/>
       <c r="BM4" s="30"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
@@ -10088,13 +10058,13 @@
       <c r="BL5" s="30"/>
       <c r="BM5" s="30"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="47" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="32">
-        <v>45964</v>
+        <v>46023</v>
       </c>
       <c r="D6" s="51"/>
       <c r="E6" s="30"/>
@@ -10103,7 +10073,7 @@
       <c r="H6" s="27"/>
       <c r="I6" s="91" t="str">
         <f ca="1">TEXT(I7,"MMMM")</f>
-        <v>November</v>
+        <v>Januar</v>
       </c>
       <c r="J6" s="91"/>
       <c r="K6" s="91"/>
@@ -10143,7 +10113,7 @@
       <c r="AJ6" s="91"/>
       <c r="AK6" s="91" t="str">
         <f ca="1">IF(OR(TEXT(AK7,"MMMM")=AD6,TEXT(AK7,"MMMM")=W6,TEXT(AK7,"MMMM")=P6,TEXT(AK7,"MMMM")=I6),"",TEXT(AK7,"MMMM"))</f>
-        <v>Dezember</v>
+        <v/>
       </c>
       <c r="AL6" s="91"/>
       <c r="AM6" s="91"/>
@@ -10153,7 +10123,7 @@
       <c r="AQ6" s="91"/>
       <c r="AR6" s="91" t="str">
         <f ca="1">IF(OR(TEXT(AR7,"MMMM")=AK6,TEXT(AR7,"MMMM")=AD6,TEXT(AR7,"MMMM")=W6,TEXT(AR7,"MMMM")=P6),"",TEXT(AR7,"MMMM"))</f>
-        <v/>
+        <v>Februar</v>
       </c>
       <c r="AS6" s="91"/>
       <c r="AT6" s="91"/>
@@ -10183,7 +10153,7 @@
       <c r="BL6" s="63"/>
       <c r="BM6" s="30"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="47" t="s">
         <v>7</v>
@@ -10198,231 +10168,231 @@
       <c r="H7" s="27"/>
       <c r="I7" s="93">
         <f ca="1">IFERROR(Projekt_Start+Scrollschrittweite,TODAY())</f>
-        <v>45965</v>
+        <v>46024</v>
       </c>
       <c r="J7" s="17">
         <f ca="1">I7+1</f>
-        <v>45966</v>
+        <v>46025</v>
       </c>
       <c r="K7" s="17">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>45967</v>
+        <v>46026</v>
       </c>
       <c r="L7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45968</v>
+        <v>46027</v>
       </c>
       <c r="M7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45969</v>
+        <v>46028</v>
       </c>
       <c r="N7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45970</v>
+        <v>46029</v>
       </c>
       <c r="O7" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>45971</v>
+        <v>46030</v>
       </c>
       <c r="P7" s="17">
         <f ca="1">O7+1</f>
-        <v>45972</v>
+        <v>46031</v>
       </c>
       <c r="Q7" s="17">
         <f ca="1">P7+1</f>
-        <v>45973</v>
+        <v>46032</v>
       </c>
       <c r="R7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45974</v>
+        <v>46033</v>
       </c>
       <c r="S7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45975</v>
+        <v>46034</v>
       </c>
       <c r="T7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45976</v>
+        <v>46035</v>
       </c>
       <c r="U7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45977</v>
+        <v>46036</v>
       </c>
       <c r="V7" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>45978</v>
+        <v>46037</v>
       </c>
       <c r="W7" s="17">
         <f ca="1">V7+1</f>
-        <v>45979</v>
+        <v>46038</v>
       </c>
       <c r="X7" s="17">
         <f ca="1">W7+1</f>
-        <v>45980</v>
+        <v>46039</v>
       </c>
       <c r="Y7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45981</v>
+        <v>46040</v>
       </c>
       <c r="Z7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45982</v>
+        <v>46041</v>
       </c>
       <c r="AA7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45983</v>
+        <v>46042</v>
       </c>
       <c r="AB7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45984</v>
+        <v>46043</v>
       </c>
       <c r="AC7" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>45985</v>
+        <v>46044</v>
       </c>
       <c r="AD7" s="17">
         <f ca="1">AC7+1</f>
-        <v>45986</v>
+        <v>46045</v>
       </c>
       <c r="AE7" s="17">
         <f ca="1">AD7+1</f>
-        <v>45987</v>
+        <v>46046</v>
       </c>
       <c r="AF7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45988</v>
+        <v>46047</v>
       </c>
       <c r="AG7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45989</v>
+        <v>46048</v>
       </c>
       <c r="AH7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45990</v>
+        <v>46049</v>
       </c>
       <c r="AI7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45991</v>
+        <v>46050</v>
       </c>
       <c r="AJ7" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>45992</v>
+        <v>46051</v>
       </c>
       <c r="AK7" s="17">
         <f ca="1">AJ7+1</f>
-        <v>45993</v>
+        <v>46052</v>
       </c>
       <c r="AL7" s="17">
         <f ca="1">AK7+1</f>
-        <v>45994</v>
+        <v>46053</v>
       </c>
       <c r="AM7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45995</v>
+        <v>46054</v>
       </c>
       <c r="AN7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45996</v>
+        <v>46055</v>
       </c>
       <c r="AO7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45997</v>
+        <v>46056</v>
       </c>
       <c r="AP7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>45998</v>
+        <v>46057</v>
       </c>
       <c r="AQ7" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>45999</v>
+        <v>46058</v>
       </c>
       <c r="AR7" s="17">
         <f ca="1">AQ7+1</f>
-        <v>46000</v>
+        <v>46059</v>
       </c>
       <c r="AS7" s="17">
         <f ca="1">AR7+1</f>
-        <v>46001</v>
+        <v>46060</v>
       </c>
       <c r="AT7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46002</v>
+        <v>46061</v>
       </c>
       <c r="AU7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46003</v>
+        <v>46062</v>
       </c>
       <c r="AV7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46004</v>
+        <v>46063</v>
       </c>
       <c r="AW7" s="17">
         <f t="shared" ca="1" si="0"/>
-        <v>46005</v>
+        <v>46064</v>
       </c>
       <c r="AX7" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>46006</v>
+        <v>46065</v>
       </c>
       <c r="AY7" s="17">
         <f ca="1">AX7+1</f>
-        <v>46007</v>
+        <v>46066</v>
       </c>
       <c r="AZ7" s="17">
         <f ca="1">AY7+1</f>
-        <v>46008</v>
+        <v>46067</v>
       </c>
       <c r="BA7" s="17">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46009</v>
+        <v>46068</v>
       </c>
       <c r="BB7" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>46010</v>
+        <v>46069</v>
       </c>
       <c r="BC7" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>46011</v>
+        <v>46070</v>
       </c>
       <c r="BD7" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>46012</v>
+        <v>46071</v>
       </c>
       <c r="BE7" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>46013</v>
+        <v>46072</v>
       </c>
       <c r="BF7" s="17">
         <f ca="1">BE7+1</f>
-        <v>46014</v>
+        <v>46073</v>
       </c>
       <c r="BG7" s="17">
         <f ca="1">BF7+1</f>
-        <v>46015</v>
+        <v>46074</v>
       </c>
       <c r="BH7" s="17">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46016</v>
+        <v>46075</v>
       </c>
       <c r="BI7" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>46017</v>
+        <v>46076</v>
       </c>
       <c r="BJ7" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>46018</v>
+        <v>46077</v>
       </c>
       <c r="BK7" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>46019</v>
+        <v>46078</v>
       </c>
       <c r="BL7" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46020</v>
+        <v>46079</v>
       </c>
       <c r="BM7" s="30"/>
     </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="49"/>
       <c r="C8" s="49"/>
@@ -10489,7 +10459,7 @@
       <c r="BL8" s="37"/>
       <c r="BM8" s="30"/>
     </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
@@ -10514,231 +10484,231 @@
       <c r="H9" s="46"/>
       <c r="I9" s="35" t="str">
         <f t="shared" ref="I9:AN9" ca="1" si="3">LEFT(TEXT(I7,"TTT"),1)</f>
-        <v>D</v>
+        <v>F</v>
       </c>
       <c r="J9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="K9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>D</v>
+        <v>S</v>
       </c>
       <c r="L9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>M</v>
       </c>
       <c r="M9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>D</v>
       </c>
       <c r="N9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="O9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="P9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>D</v>
+        <v>F</v>
       </c>
       <c r="Q9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="R9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>D</v>
+        <v>S</v>
       </c>
       <c r="S9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>M</v>
       </c>
       <c r="T9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>D</v>
       </c>
       <c r="U9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="V9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="W9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>D</v>
+        <v>F</v>
       </c>
       <c r="X9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="Y9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>D</v>
+        <v>S</v>
       </c>
       <c r="Z9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>M</v>
       </c>
       <c r="AA9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>D</v>
       </c>
       <c r="AB9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AC9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="AD9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>D</v>
+        <v>F</v>
       </c>
       <c r="AE9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AF9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>D</v>
+        <v>S</v>
       </c>
       <c r="AG9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>M</v>
       </c>
       <c r="AH9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>D</v>
       </c>
       <c r="AI9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AJ9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="AK9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>D</v>
+        <v>F</v>
       </c>
       <c r="AL9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AM9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>D</v>
+        <v>S</v>
       </c>
       <c r="AN9" s="35" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>M</v>
       </c>
       <c r="AO9" s="35" t="str">
         <f t="shared" ref="AO9:BL9" ca="1" si="4">LEFT(TEXT(AO7,"TTT"),1)</f>
-        <v>S</v>
+        <v>D</v>
       </c>
       <c r="AP9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AQ9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="AR9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>D</v>
+        <v>F</v>
       </c>
       <c r="AS9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AT9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>D</v>
+        <v>S</v>
       </c>
       <c r="AU9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>F</v>
+        <v>M</v>
       </c>
       <c r="AV9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>D</v>
       </c>
       <c r="AW9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AX9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="AY9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>D</v>
+        <v>F</v>
       </c>
       <c r="AZ9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="BA9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>D</v>
+        <v>S</v>
       </c>
       <c r="BB9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>F</v>
+        <v>M</v>
       </c>
       <c r="BC9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>D</v>
       </c>
       <c r="BD9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BE9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="BF9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>D</v>
+        <v>F</v>
       </c>
       <c r="BG9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="BH9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>D</v>
+        <v>S</v>
       </c>
       <c r="BI9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>F</v>
+        <v>M</v>
       </c>
       <c r="BJ9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>D</v>
       </c>
       <c r="BK9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BL9" s="35" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>M</v>
+        <v>D</v>
       </c>
       <c r="BM9" s="30"/>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="16"/>
       <c r="C10" s="13"/>
       <c r="D10" s="12"/>
@@ -10804,7 +10774,7 @@
       <c r="BL10" s="34"/>
       <c r="BM10" s="30"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="120" t="s">
         <v>38</v>
@@ -11045,25 +11015,21 @@
       </c>
       <c r="BP11" s="39"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="121" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="22">
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="23">
+        <v>46028</v>
+      </c>
+      <c r="G12" s="24">
         <v>1</v>
-      </c>
-      <c r="F12" s="23">
-        <v>45965</v>
-      </c>
-      <c r="G12" s="24">
-        <v>7</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12" s="45" t="str">
@@ -11295,24 +11261,16 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="121"/>
       <c r="C13" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="22">
-        <v>1</v>
-      </c>
-      <c r="F13" s="23">
-        <v>45965</v>
-      </c>
-      <c r="G13" s="24">
-        <v>1</v>
-      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="19"/>
       <c r="I13" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -11543,25 +11501,21 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="121" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="22">
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23">
+        <v>46030</v>
+      </c>
+      <c r="G14" s="24">
         <v>1</v>
-      </c>
-      <c r="F14" s="23">
-        <v>45971</v>
-      </c>
-      <c r="G14" s="24">
-        <v>2</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="45" t="str">
@@ -11793,24 +11747,16 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="121"/>
       <c r="C15" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="22">
-        <v>1</v>
-      </c>
-      <c r="F15" s="23">
-        <v>45966</v>
-      </c>
-      <c r="G15" s="24">
-        <v>9</v>
-      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="19"/>
       <c r="I15" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -12041,25 +11987,21 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="121" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="22">
-        <v>0.8</v>
-      </c>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="23">
-        <v>45972</v>
+        <v>46034</v>
       </c>
       <c r="G16" s="24">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="45" t="str">
@@ -12291,24 +12233,16 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="121"/>
       <c r="C17" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="22">
-        <v>0.8</v>
-      </c>
-      <c r="F17" s="23">
-        <v>45974</v>
-      </c>
-      <c r="G17" s="24">
-        <v>7</v>
-      </c>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="19"/>
       <c r="I17" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -12539,22 +12473,18 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="121" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="22">
-        <v>1</v>
-      </c>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
       <c r="F18" s="23">
-        <v>45981</v>
+        <v>46035</v>
       </c>
       <c r="G18" s="24">
         <v>1</v>
@@ -12789,24 +12719,16 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="B19" s="12"/>
       <c r="C19" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="22">
-        <v>1</v>
-      </c>
-      <c r="F19" s="23">
-        <v>45981</v>
-      </c>
-      <c r="G19" s="24">
-        <v>5</v>
-      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="19"/>
       <c r="I19" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -13037,25 +12959,21 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="121" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="22">
-        <v>1</v>
-      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
       <c r="F20" s="23">
-        <v>45986</v>
+        <v>46041</v>
       </c>
       <c r="G20" s="24">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H20" s="19"/>
       <c r="I20" s="45" t="str">
@@ -13287,24 +13205,16 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
-      <c r="B21" s="124"/>
+      <c r="B21" s="121"/>
       <c r="C21" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" s="22">
-        <v>1</v>
-      </c>
-      <c r="F21" s="23">
-        <v>45986</v>
-      </c>
-      <c r="G21" s="24">
-        <v>1</v>
-      </c>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="19"/>
       <c r="I21" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -13535,26 +13445,16 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
-      <c r="B22" s="121" t="s">
-        <v>64</v>
-      </c>
+      <c r="B22" s="121"/>
       <c r="C22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="22">
-        <v>0</v>
-      </c>
-      <c r="F22" s="23">
-        <v>45993</v>
-      </c>
-      <c r="G22" s="24">
-        <v>1</v>
-      </c>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="19"/>
       <c r="I22" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -13785,24 +13685,16 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="121"/>
       <c r="C23" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="22">
-        <v>0</v>
-      </c>
-      <c r="F23" s="23">
-        <v>45993</v>
-      </c>
-      <c r="G23" s="24">
-        <v>1</v>
-      </c>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="24"/>
       <c r="H23" s="19"/>
       <c r="I23" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14033,26 +13925,16 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
-      <c r="B24" s="121" t="s">
-        <v>65</v>
-      </c>
+      <c r="B24" s="121"/>
       <c r="C24" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="22">
-        <v>0</v>
-      </c>
-      <c r="F24" s="23">
-        <v>45995</v>
-      </c>
-      <c r="G24" s="24">
-        <v>7</v>
-      </c>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="24"/>
       <c r="H24" s="19"/>
       <c r="I24" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -14283,19 +14165,15 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="121"/>
       <c r="C25" s="21" t="s">
         <v>42</v>
       </c>
       <c r="D25" s="21"/>
-      <c r="E25" s="22">
-        <v>0</v>
-      </c>
-      <c r="F25" s="23">
-        <v>45995</v>
-      </c>
+      <c r="E25" s="22"/>
+      <c r="F25" s="23"/>
       <c r="G25" s="24"/>
       <c r="H25" s="19"/>
       <c r="I25" s="45" t="str">
@@ -14527,26 +14405,16 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
-      <c r="B26" s="121" t="s">
-        <v>49</v>
-      </c>
+      <c r="B26" s="121"/>
       <c r="C26" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="22">
-        <v>0</v>
-      </c>
-      <c r="F26" s="23">
-        <v>46001</v>
-      </c>
-      <c r="G26" s="24">
-        <v>7</v>
-      </c>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="24"/>
       <c r="H26" s="19"/>
       <c r="I26" s="45" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -14777,7 +14645,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="121"/>
       <c r="C27" s="21" t="s">
@@ -15017,11 +14885,9 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
-      <c r="B28" s="121" t="s">
-        <v>50</v>
-      </c>
+      <c r="B28" s="12"/>
       <c r="C28" s="21" t="s">
         <v>41</v>
       </c>
@@ -15259,7 +15125,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
       <c r="B29" s="121"/>
       <c r="C29" s="21" t="s">
@@ -15499,11 +15365,9 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
-      <c r="B30" s="121" t="s">
-        <v>51</v>
-      </c>
+      <c r="B30" s="121"/>
       <c r="C30" s="21" t="s">
         <v>42</v>
       </c>
@@ -15741,7 +15605,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
       <c r="B31" s="121"/>
       <c r="C31" s="21" t="s">
@@ -15981,7 +15845,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="121"/>
       <c r="C32" s="21" t="s">
@@ -16221,7 +16085,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="121"/>
       <c r="C33" s="21" t="s">
@@ -16461,7 +16325,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
       <c r="B34" s="121"/>
       <c r="C34" s="21" t="s">
@@ -16701,7 +16565,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
       <c r="B35" s="121"/>
       <c r="C35" s="21" t="s">
@@ -16941,7 +16805,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="114" t="s">
         <v>18</v>
@@ -17010,12 +16874,12 @@
       <c r="BL36" s="54"/>
       <c r="BM36" s="26"/>
     </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="4"/>
       <c r="G37" s="11"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="5"/>
     </row>
   </sheetData>
@@ -17179,44 +17043,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.73046875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="37.86328125" customWidth="1"/>
-    <col min="3" max="3" width="15.265625" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" customWidth="1"/>
-    <col min="5" max="5" width="15.73046875" customWidth="1"/>
-    <col min="6" max="6" width="10.3984375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" customWidth="1"/>
-    <col min="8" max="8" width="2.73046875" customWidth="1"/>
-    <col min="9" max="64" width="3.59765625" customWidth="1"/>
-    <col min="65" max="65" width="2.73046875" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="37.85546875" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" customWidth="1"/>
+    <col min="9" max="64" width="3.5703125" customWidth="1"/>
+    <col min="65" max="65" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="140" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="142"/>
-      <c r="M2" s="142"/>
-      <c r="N2" s="142"/>
-      <c r="O2" s="143"/>
-      <c r="P2" s="143"/>
-      <c r="Q2" s="143"/>
-      <c r="R2" s="143"/>
-      <c r="S2" s="143"/>
-      <c r="T2" s="143"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="142"/>
+      <c r="P2" s="142"/>
+      <c r="Q2" s="142"/>
+      <c r="R2" s="142"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="142"/>
       <c r="U2" s="94"/>
       <c r="V2" s="94"/>
       <c r="W2" s="94"/>
@@ -17263,7 +17127,7 @@
       <c r="BL2" s="94"/>
       <c r="BM2" s="94"/>
     </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="65"/>
       <c r="C3" s="66"/>
@@ -17277,7 +17141,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="69" t="s">
         <v>4</v>
@@ -17290,48 +17154,48 @@
         <v>30</v>
       </c>
       <c r="H4" s="72"/>
-      <c r="I4" s="131" t="s">
+      <c r="I4" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
-      <c r="P4" s="138" t="s">
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="P4" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="Q4" s="138"/>
-      <c r="R4" s="138"/>
-      <c r="S4" s="138"/>
-      <c r="T4" s="138"/>
-      <c r="U4" s="138"/>
-      <c r="W4" s="139" t="s">
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
+      <c r="W4" s="138" t="s">
         <v>23</v>
       </c>
-      <c r="X4" s="139"/>
-      <c r="Y4" s="139"/>
-      <c r="Z4" s="139"/>
-      <c r="AA4" s="139"/>
-      <c r="AB4" s="139"/>
-      <c r="AD4" s="140" t="s">
+      <c r="X4" s="138"/>
+      <c r="Y4" s="138"/>
+      <c r="Z4" s="138"/>
+      <c r="AA4" s="138"/>
+      <c r="AB4" s="138"/>
+      <c r="AD4" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="AE4" s="140"/>
-      <c r="AF4" s="140"/>
-      <c r="AG4" s="140"/>
-      <c r="AH4" s="140"/>
-      <c r="AJ4" s="133" t="s">
+      <c r="AE4" s="139"/>
+      <c r="AF4" s="139"/>
+      <c r="AG4" s="139"/>
+      <c r="AH4" s="139"/>
+      <c r="AJ4" s="132" t="s">
         <v>33</v>
       </c>
-      <c r="AK4" s="133"/>
-      <c r="AL4" s="133"/>
-      <c r="AM4" s="133"/>
-      <c r="AN4" s="133"/>
-      <c r="AO4" s="133"/>
-      <c r="AP4" s="133"/>
+      <c r="AK4" s="132"/>
+      <c r="AL4" s="132"/>
+      <c r="AM4" s="132"/>
+      <c r="AN4" s="132"/>
+      <c r="AO4" s="132"/>
+      <c r="AP4" s="132"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
@@ -17345,14 +17209,14 @@
       <c r="G5" s="72"/>
       <c r="H5" s="72"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="76" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="77" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Meilensteine43524[Start])=0,TODAY(),B11(Meilensteine43524[Start])),TODAY())</f>
-        <v>46007</v>
+        <v>46028</v>
       </c>
       <c r="D6" s="78"/>
       <c r="E6" s="72"/>
@@ -17361,7 +17225,7 @@
       <c r="H6" s="72"/>
       <c r="I6" s="88" t="str">
         <f ca="1">TEXT(I7,"MMMM")</f>
-        <v>Dezember</v>
+        <v>Januar</v>
       </c>
       <c r="J6" s="88"/>
       <c r="K6" s="88"/>
@@ -17391,7 +17255,7 @@
       <c r="AC6" s="88"/>
       <c r="AD6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(AD7,"MMMM")=W6,TEXT(AD7,"MMMM")=P6,TEXT(AD7,"MMMM")=I6),"",TEXT(AD7,"MMMM"))</f>
-        <v>Januar</v>
+        <v/>
       </c>
       <c r="AE6" s="88"/>
       <c r="AF6" s="88"/>
@@ -17401,7 +17265,7 @@
       <c r="AJ6" s="88"/>
       <c r="AK6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(AK7,"MMMM")=AD6,TEXT(AK7,"MMMM")=W6,TEXT(AK7,"MMMM")=P6,TEXT(AK7,"MMMM")=I6),"",TEXT(AK7,"MMMM"))</f>
-        <v/>
+        <v>Februar</v>
       </c>
       <c r="AL6" s="88"/>
       <c r="AM6" s="88"/>
@@ -17431,7 +17295,7 @@
       <c r="BE6" s="87"/>
       <c r="BF6" s="87" t="str">
         <f ca="1">IF(OR(TEXT(BF7,"MMMM")=AY6,TEXT(BF7,"MMMM")=AR6,TEXT(BF7,"MMMM")=AK6,TEXT(BF7,"MMMM")=AD6),"",TEXT(BF7,"MMMM"))</f>
-        <v>Februar</v>
+        <v/>
       </c>
       <c r="BG6" s="87"/>
       <c r="BH6" s="87"/>
@@ -17440,7 +17304,7 @@
       <c r="BK6" s="87"/>
       <c r="BL6" s="87"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="76" t="s">
         <v>7</v>
@@ -17455,230 +17319,230 @@
       <c r="H7" s="80"/>
       <c r="I7" s="95">
         <f ca="1">IFERROR(Projekt_Start+Scrollschrittweite,TODAY())</f>
-        <v>46008</v>
+        <v>46029</v>
       </c>
       <c r="J7" s="96">
         <f ca="1">I7+1</f>
-        <v>46009</v>
+        <v>46030</v>
       </c>
       <c r="K7" s="96">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46010</v>
+        <v>46031</v>
       </c>
       <c r="L7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46011</v>
+        <v>46032</v>
       </c>
       <c r="M7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46012</v>
+        <v>46033</v>
       </c>
       <c r="N7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46013</v>
+        <v>46034</v>
       </c>
       <c r="O7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46014</v>
+        <v>46035</v>
       </c>
       <c r="P7" s="96">
         <f ca="1">O7+1</f>
-        <v>46015</v>
+        <v>46036</v>
       </c>
       <c r="Q7" s="96">
         <f ca="1">P7+1</f>
-        <v>46016</v>
+        <v>46037</v>
       </c>
       <c r="R7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46017</v>
+        <v>46038</v>
       </c>
       <c r="S7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46018</v>
+        <v>46039</v>
       </c>
       <c r="T7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46019</v>
+        <v>46040</v>
       </c>
       <c r="U7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46020</v>
+        <v>46041</v>
       </c>
       <c r="V7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46021</v>
+        <v>46042</v>
       </c>
       <c r="W7" s="96">
         <f ca="1">V7+1</f>
-        <v>46022</v>
+        <v>46043</v>
       </c>
       <c r="X7" s="96">
         <f ca="1">W7+1</f>
-        <v>46023</v>
+        <v>46044</v>
       </c>
       <c r="Y7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46024</v>
+        <v>46045</v>
       </c>
       <c r="Z7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46025</v>
+        <v>46046</v>
       </c>
       <c r="AA7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46026</v>
+        <v>46047</v>
       </c>
       <c r="AB7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46027</v>
+        <v>46048</v>
       </c>
       <c r="AC7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46028</v>
+        <v>46049</v>
       </c>
       <c r="AD7" s="96">
         <f ca="1">AC7+1</f>
-        <v>46029</v>
+        <v>46050</v>
       </c>
       <c r="AE7" s="96">
         <f ca="1">AD7+1</f>
-        <v>46030</v>
+        <v>46051</v>
       </c>
       <c r="AF7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46031</v>
+        <v>46052</v>
       </c>
       <c r="AG7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46032</v>
+        <v>46053</v>
       </c>
       <c r="AH7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46033</v>
+        <v>46054</v>
       </c>
       <c r="AI7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46034</v>
+        <v>46055</v>
       </c>
       <c r="AJ7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46035</v>
+        <v>46056</v>
       </c>
       <c r="AK7" s="96">
         <f ca="1">AJ7+1</f>
-        <v>46036</v>
+        <v>46057</v>
       </c>
       <c r="AL7" s="96">
         <f ca="1">AK7+1</f>
-        <v>46037</v>
+        <v>46058</v>
       </c>
       <c r="AM7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46038</v>
+        <v>46059</v>
       </c>
       <c r="AN7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46039</v>
+        <v>46060</v>
       </c>
       <c r="AO7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46040</v>
+        <v>46061</v>
       </c>
       <c r="AP7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46041</v>
+        <v>46062</v>
       </c>
       <c r="AQ7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46042</v>
+        <v>46063</v>
       </c>
       <c r="AR7" s="96">
         <f ca="1">AQ7+1</f>
-        <v>46043</v>
+        <v>46064</v>
       </c>
       <c r="AS7" s="96">
         <f ca="1">AR7+1</f>
-        <v>46044</v>
+        <v>46065</v>
       </c>
       <c r="AT7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46045</v>
+        <v>46066</v>
       </c>
       <c r="AU7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46046</v>
+        <v>46067</v>
       </c>
       <c r="AV7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46047</v>
+        <v>46068</v>
       </c>
       <c r="AW7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46048</v>
+        <v>46069</v>
       </c>
       <c r="AX7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46049</v>
+        <v>46070</v>
       </c>
       <c r="AY7" s="96">
         <f ca="1">AX7+1</f>
-        <v>46050</v>
+        <v>46071</v>
       </c>
       <c r="AZ7" s="96">
         <f ca="1">AY7+1</f>
-        <v>46051</v>
+        <v>46072</v>
       </c>
       <c r="BA7" s="96">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46052</v>
+        <v>46073</v>
       </c>
       <c r="BB7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46053</v>
+        <v>46074</v>
       </c>
       <c r="BC7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46054</v>
+        <v>46075</v>
       </c>
       <c r="BD7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46055</v>
+        <v>46076</v>
       </c>
       <c r="BE7" s="97">
         <f t="shared" ca="1" si="1"/>
-        <v>46056</v>
+        <v>46077</v>
       </c>
       <c r="BF7" s="96">
         <f ca="1">BE7+1</f>
-        <v>46057</v>
+        <v>46078</v>
       </c>
       <c r="BG7" s="96">
         <f ca="1">BF7+1</f>
-        <v>46058</v>
+        <v>46079</v>
       </c>
       <c r="BH7" s="96">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46059</v>
+        <v>46080</v>
       </c>
       <c r="BI7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46060</v>
+        <v>46081</v>
       </c>
       <c r="BJ7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46061</v>
+        <v>46082</v>
       </c>
       <c r="BK7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46062</v>
+        <v>46083</v>
       </c>
       <c r="BL7" s="97">
         <f t="shared" ca="1" si="2"/>
-        <v>46063</v>
+        <v>46084</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="71"/>
       <c r="C8" s="71"/>
@@ -17744,7 +17608,7 @@
       <c r="BK8" s="99"/>
       <c r="BL8" s="102"/>
     </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
@@ -17992,7 +17856,7 @@
         <v>D</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="16"/>
       <c r="C10" s="13"/>
       <c r="D10" s="12"/>
@@ -18056,7 +17920,7 @@
       <c r="BK10" s="34"/>
       <c r="BL10" s="34"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="113" t="s">
         <v>9</v>
@@ -18293,7 +18157,7 @@
       </c>
       <c r="BP11" s="39"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="61" t="s">
         <v>10</v>
@@ -18309,7 +18173,7 @@
       </c>
       <c r="F12" s="59">
         <f ca="1">TODAY()</f>
-        <v>46007</v>
+        <v>46028</v>
       </c>
       <c r="G12" s="60">
         <v>3</v>
@@ -18540,7 +18404,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="61" t="s">
         <v>11</v>
@@ -18552,7 +18416,7 @@
       <c r="E13" s="58"/>
       <c r="F13" s="59">
         <f ca="1">TODAY()+5</f>
-        <v>46012</v>
+        <v>46033</v>
       </c>
       <c r="G13" s="60">
         <v>1</v>
@@ -18783,7 +18647,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="61" t="s">
         <v>12</v>
@@ -18797,7 +18661,7 @@
       </c>
       <c r="F14" s="59">
         <f ca="1">F12-3</f>
-        <v>46004</v>
+        <v>46025</v>
       </c>
       <c r="G14" s="60">
         <v>10</v>
@@ -19028,7 +18892,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="61" t="s">
         <v>13</v>
@@ -19040,7 +18904,7 @@
       <c r="E15" s="58"/>
       <c r="F15" s="59">
         <f ca="1">F12+20</f>
-        <v>46027</v>
+        <v>46048</v>
       </c>
       <c r="G15" s="60">
         <v>1</v>
@@ -19271,7 +19135,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="B16" s="61" t="s">
         <v>14</v>
@@ -19285,7 +19149,7 @@
       </c>
       <c r="F16" s="59">
         <f ca="1">F12+6</f>
-        <v>46013</v>
+        <v>46034</v>
       </c>
       <c r="G16" s="60">
         <v>6</v>
@@ -19516,7 +19380,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="113" t="s">
         <v>15</v>
@@ -19752,7 +19616,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="61" t="s">
         <v>10</v>
@@ -19766,7 +19630,7 @@
       </c>
       <c r="F18" s="59">
         <f ca="1">F12+6</f>
-        <v>46013</v>
+        <v>46034</v>
       </c>
       <c r="G18" s="60">
         <v>13</v>
@@ -19997,7 +19861,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="B19" s="61" t="s">
         <v>11</v>
@@ -20011,7 +19875,7 @@
       </c>
       <c r="F19" s="59">
         <f ca="1">F18+2</f>
-        <v>46015</v>
+        <v>46036</v>
       </c>
       <c r="G19" s="60">
         <v>9</v>
@@ -20242,7 +20106,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
       <c r="B20" s="61" t="s">
         <v>12</v>
@@ -20256,7 +20120,7 @@
       </c>
       <c r="F20" s="59">
         <f ca="1">F19+5</f>
-        <v>46020</v>
+        <v>46041</v>
       </c>
       <c r="G20" s="60">
         <v>11</v>
@@ -20487,7 +20351,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9"/>
       <c r="B21" s="61" t="s">
         <v>13</v>
@@ -20499,7 +20363,7 @@
       <c r="E21" s="58"/>
       <c r="F21" s="59">
         <f ca="1">F20+2</f>
-        <v>46022</v>
+        <v>46043</v>
       </c>
       <c r="G21" s="60">
         <v>1</v>
@@ -20730,7 +20594,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9"/>
       <c r="B22" s="61" t="s">
         <v>14</v>
@@ -20740,7 +20604,7 @@
       <c r="E22" s="58"/>
       <c r="F22" s="59">
         <f ca="1">F21+1</f>
-        <v>46023</v>
+        <v>46044</v>
       </c>
       <c r="G22" s="60">
         <v>24</v>
@@ -20971,7 +20835,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="113" t="s">
         <v>16</v>
@@ -21207,7 +21071,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9"/>
       <c r="B24" s="61" t="s">
         <v>10</v>
@@ -21219,7 +21083,7 @@
       <c r="E24" s="58"/>
       <c r="F24" s="59">
         <f ca="1">F12+15</f>
-        <v>46022</v>
+        <v>46043</v>
       </c>
       <c r="G24" s="60">
         <v>4</v>
@@ -21450,7 +21314,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
       <c r="B25" s="61" t="s">
         <v>11</v>
@@ -21462,7 +21326,7 @@
       <c r="E25" s="58"/>
       <c r="F25" s="59">
         <f ca="1">F24+3</f>
-        <v>46025</v>
+        <v>46046</v>
       </c>
       <c r="G25" s="60">
         <v>14</v>
@@ -21693,7 +21557,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="B26" s="61" t="s">
         <v>12</v>
@@ -21705,7 +21569,7 @@
       <c r="E26" s="58"/>
       <c r="F26" s="59">
         <f ca="1">F25+15</f>
-        <v>46040</v>
+        <v>46061</v>
       </c>
       <c r="G26" s="60">
         <v>6</v>
@@ -21936,7 +21800,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="61" t="s">
         <v>13</v>
@@ -21948,7 +21812,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="59">
         <f ca="1">F21+22</f>
-        <v>46044</v>
+        <v>46065</v>
       </c>
       <c r="G27" s="60">
         <v>3</v>
@@ -22179,7 +22043,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
       <c r="B28" s="61" t="s">
         <v>14</v>
@@ -22191,7 +22055,7 @@
       <c r="E28" s="58"/>
       <c r="F28" s="59">
         <f ca="1">F16</f>
-        <v>46013</v>
+        <v>46034</v>
       </c>
       <c r="G28" s="60">
         <v>19</v>
@@ -22422,7 +22286,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
       <c r="B29" s="113" t="s">
         <v>17</v>
@@ -22658,7 +22522,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
       <c r="B30" s="61" t="s">
         <v>10</v>
@@ -22668,7 +22532,7 @@
       <c r="E30" s="58"/>
       <c r="F30" s="59">
         <f ca="1">F27+3</f>
-        <v>46047</v>
+        <v>46068</v>
       </c>
       <c r="G30" s="60">
         <v>15</v>
@@ -22899,7 +22763,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
       <c r="B31" s="61" t="s">
         <v>11</v>
@@ -22909,7 +22773,7 @@
       <c r="E31" s="58"/>
       <c r="F31" s="59">
         <f ca="1">F30+14</f>
-        <v>46061</v>
+        <v>46082</v>
       </c>
       <c r="G31" s="60">
         <v>5</v>
@@ -23140,7 +23004,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="61" t="s">
         <v>12</v>
@@ -23152,7 +23016,7 @@
       <c r="E32" s="58"/>
       <c r="F32" s="59">
         <f ca="1">F31+42</f>
-        <v>46103</v>
+        <v>46124</v>
       </c>
       <c r="G32" s="60">
         <v>1</v>
@@ -23383,7 +23247,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="61" t="s">
         <v>13</v>
@@ -23619,7 +23483,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
       <c r="B34" s="61" t="s">
         <v>14</v>
@@ -23855,7 +23719,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
       <c r="B35" s="61"/>
       <c r="C35" s="57"/>
@@ -24090,7 +23954,7 @@
       </c>
       <c r="BM35" s="86"/>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10"/>
       <c r="B36" s="115" t="s">
         <v>18</v>
@@ -24158,12 +24022,12 @@
       <c r="BK36" s="84"/>
       <c r="BL36" s="84"/>
     </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="4"/>
       <c r="G37" s="11"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="5"/>
     </row>
   </sheetData>
@@ -24615,6 +24479,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -24632,15 +24505,6 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24665,6 +24529,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAF2F40C-D12E-4644-AA6E-31E499F048DC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CD6AD73-D703-40CF-AB8D-72E6A3921BEB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -24674,12 +24546,4 @@
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAF2F40C-D12E-4644-AA6E-31E499F048DC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Diagramme/SmartClock_Gantt-Diagramm_V2.xlsx
+++ b/Diagramme/SmartClock_Gantt-Diagramm_V2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="684" documentId="8_{0C4EAEB1-A5C4-4402-980F-B32D81185735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE44A00B-A8B7-455F-BA14-85B51F32F1F8}"/>
+  <xr:revisionPtr revIDLastSave="697" documentId="8_{0C4EAEB1-A5C4-4402-980F-B32D81185735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64EE4A6D-F461-4C5D-B572-20DCEA631B00}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-1665" windowWidth="29040" windowHeight="15720" tabRatio="415" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11269,8 +11269,12 @@
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="22"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="24"/>
+      <c r="F13" s="23">
+        <v>46028</v>
+      </c>
+      <c r="G13" s="24">
+        <v>1</v>
+      </c>
       <c r="H13" s="19"/>
       <c r="I13" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -11755,8 +11759,12 @@
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="22"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="24"/>
+      <c r="F15" s="23">
+        <v>46028</v>
+      </c>
+      <c r="G15" s="24">
+        <v>1</v>
+      </c>
       <c r="H15" s="19"/>
       <c r="I15" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -12241,8 +12249,12 @@
       </c>
       <c r="D17" s="21"/>
       <c r="E17" s="22"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="24"/>
+      <c r="F17" s="23">
+        <v>46028</v>
+      </c>
+      <c r="G17" s="24">
+        <v>1</v>
+      </c>
       <c r="H17" s="19"/>
       <c r="I17" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -12727,8 +12739,12 @@
       </c>
       <c r="D19" s="21"/>
       <c r="E19" s="22"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="24"/>
+      <c r="F19" s="23">
+        <v>46028</v>
+      </c>
+      <c r="G19" s="24">
+        <v>1</v>
+      </c>
       <c r="H19" s="19"/>
       <c r="I19" s="45" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -17216,7 +17232,7 @@
       </c>
       <c r="C6" s="77" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Meilensteine43524[Start])=0,TODAY(),B11(Meilensteine43524[Start])),TODAY())</f>
-        <v>46028</v>
+        <v>46035</v>
       </c>
       <c r="D6" s="78"/>
       <c r="E6" s="72"/>
@@ -17255,7 +17271,7 @@
       <c r="AC6" s="88"/>
       <c r="AD6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(AD7,"MMMM")=W6,TEXT(AD7,"MMMM")=P6,TEXT(AD7,"MMMM")=I6),"",TEXT(AD7,"MMMM"))</f>
-        <v/>
+        <v>Februar</v>
       </c>
       <c r="AE6" s="88"/>
       <c r="AF6" s="88"/>
@@ -17265,7 +17281,7 @@
       <c r="AJ6" s="88"/>
       <c r="AK6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(AK7,"MMMM")=AD6,TEXT(AK7,"MMMM")=W6,TEXT(AK7,"MMMM")=P6,TEXT(AK7,"MMMM")=I6),"",TEXT(AK7,"MMMM"))</f>
-        <v>Februar</v>
+        <v/>
       </c>
       <c r="AL6" s="88"/>
       <c r="AM6" s="88"/>
@@ -17295,7 +17311,7 @@
       <c r="BE6" s="87"/>
       <c r="BF6" s="87" t="str">
         <f ca="1">IF(OR(TEXT(BF7,"MMMM")=AY6,TEXT(BF7,"MMMM")=AR6,TEXT(BF7,"MMMM")=AK6,TEXT(BF7,"MMMM")=AD6),"",TEXT(BF7,"MMMM"))</f>
-        <v/>
+        <v>März</v>
       </c>
       <c r="BG6" s="87"/>
       <c r="BH6" s="87"/>
@@ -17319,227 +17335,227 @@
       <c r="H7" s="80"/>
       <c r="I7" s="95">
         <f ca="1">IFERROR(Projekt_Start+Scrollschrittweite,TODAY())</f>
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="J7" s="96">
         <f ca="1">I7+1</f>
-        <v>46030</v>
+        <v>46037</v>
       </c>
       <c r="K7" s="96">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="L7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46032</v>
+        <v>46039</v>
       </c>
       <c r="M7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46033</v>
+        <v>46040</v>
       </c>
       <c r="N7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="O7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46035</v>
+        <v>46042</v>
       </c>
       <c r="P7" s="96">
         <f ca="1">O7+1</f>
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="Q7" s="96">
         <f ca="1">P7+1</f>
-        <v>46037</v>
+        <v>46044</v>
       </c>
       <c r="R7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="S7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46039</v>
+        <v>46046</v>
       </c>
       <c r="T7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46040</v>
+        <v>46047</v>
       </c>
       <c r="U7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="V7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46042</v>
+        <v>46049</v>
       </c>
       <c r="W7" s="96">
         <f ca="1">V7+1</f>
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="X7" s="96">
         <f ca="1">W7+1</f>
-        <v>46044</v>
+        <v>46051</v>
       </c>
       <c r="Y7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46045</v>
+        <v>46052</v>
       </c>
       <c r="Z7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46046</v>
+        <v>46053</v>
       </c>
       <c r="AA7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46047</v>
+        <v>46054</v>
       </c>
       <c r="AB7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="AC7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="AD7" s="96">
         <f ca="1">AC7+1</f>
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="AE7" s="96">
         <f ca="1">AD7+1</f>
-        <v>46051</v>
+        <v>46058</v>
       </c>
       <c r="AF7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46052</v>
+        <v>46059</v>
       </c>
       <c r="AG7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46053</v>
+        <v>46060</v>
       </c>
       <c r="AH7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46054</v>
+        <v>46061</v>
       </c>
       <c r="AI7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="AJ7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46056</v>
+        <v>46063</v>
       </c>
       <c r="AK7" s="96">
         <f ca="1">AJ7+1</f>
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="AL7" s="96">
         <f ca="1">AK7+1</f>
-        <v>46058</v>
+        <v>46065</v>
       </c>
       <c r="AM7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46066</v>
       </c>
       <c r="AN7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46060</v>
+        <v>46067</v>
       </c>
       <c r="AO7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46061</v>
+        <v>46068</v>
       </c>
       <c r="AP7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="AQ7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46063</v>
+        <v>46070</v>
       </c>
       <c r="AR7" s="96">
         <f ca="1">AQ7+1</f>
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="AS7" s="96">
         <f ca="1">AR7+1</f>
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="AT7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46066</v>
+        <v>46073</v>
       </c>
       <c r="AU7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46067</v>
+        <v>46074</v>
       </c>
       <c r="AV7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46068</v>
+        <v>46075</v>
       </c>
       <c r="AW7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46069</v>
+        <v>46076</v>
       </c>
       <c r="AX7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46070</v>
+        <v>46077</v>
       </c>
       <c r="AY7" s="96">
         <f ca="1">AX7+1</f>
-        <v>46071</v>
+        <v>46078</v>
       </c>
       <c r="AZ7" s="96">
         <f ca="1">AY7+1</f>
-        <v>46072</v>
+        <v>46079</v>
       </c>
       <c r="BA7" s="96">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46073</v>
+        <v>46080</v>
       </c>
       <c r="BB7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46074</v>
+        <v>46081</v>
       </c>
       <c r="BC7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46075</v>
+        <v>46082</v>
       </c>
       <c r="BD7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="BE7" s="97">
         <f t="shared" ca="1" si="1"/>
-        <v>46077</v>
+        <v>46084</v>
       </c>
       <c r="BF7" s="96">
         <f ca="1">BE7+1</f>
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="BG7" s="96">
         <f ca="1">BF7+1</f>
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="BH7" s="96">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="BI7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46081</v>
+        <v>46088</v>
       </c>
       <c r="BJ7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46082</v>
+        <v>46089</v>
       </c>
       <c r="BK7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="BL7" s="97">
         <f t="shared" ca="1" si="2"/>
-        <v>46084</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -18173,7 +18189,7 @@
       </c>
       <c r="F12" s="59">
         <f ca="1">TODAY()</f>
-        <v>46028</v>
+        <v>46035</v>
       </c>
       <c r="G12" s="60">
         <v>3</v>
@@ -18416,7 +18432,7 @@
       <c r="E13" s="58"/>
       <c r="F13" s="59">
         <f ca="1">TODAY()+5</f>
-        <v>46033</v>
+        <v>46040</v>
       </c>
       <c r="G13" s="60">
         <v>1</v>
@@ -18661,7 +18677,7 @@
       </c>
       <c r="F14" s="59">
         <f ca="1">F12-3</f>
-        <v>46025</v>
+        <v>46032</v>
       </c>
       <c r="G14" s="60">
         <v>10</v>
@@ -18904,7 +18920,7 @@
       <c r="E15" s="58"/>
       <c r="F15" s="59">
         <f ca="1">F12+20</f>
-        <v>46048</v>
+        <v>46055</v>
       </c>
       <c r="G15" s="60">
         <v>1</v>
@@ -19149,7 +19165,7 @@
       </c>
       <c r="F16" s="59">
         <f ca="1">F12+6</f>
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="G16" s="60">
         <v>6</v>
@@ -19630,7 +19646,7 @@
       </c>
       <c r="F18" s="59">
         <f ca="1">F12+6</f>
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="G18" s="60">
         <v>13</v>
@@ -19875,7 +19891,7 @@
       </c>
       <c r="F19" s="59">
         <f ca="1">F18+2</f>
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="G19" s="60">
         <v>9</v>
@@ -20120,7 +20136,7 @@
       </c>
       <c r="F20" s="59">
         <f ca="1">F19+5</f>
-        <v>46041</v>
+        <v>46048</v>
       </c>
       <c r="G20" s="60">
         <v>11</v>
@@ -20363,7 +20379,7 @@
       <c r="E21" s="58"/>
       <c r="F21" s="59">
         <f ca="1">F20+2</f>
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="G21" s="60">
         <v>1</v>
@@ -20604,7 +20620,7 @@
       <c r="E22" s="58"/>
       <c r="F22" s="59">
         <f ca="1">F21+1</f>
-        <v>46044</v>
+        <v>46051</v>
       </c>
       <c r="G22" s="60">
         <v>24</v>
@@ -21083,7 +21099,7 @@
       <c r="E24" s="58"/>
       <c r="F24" s="59">
         <f ca="1">F12+15</f>
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="G24" s="60">
         <v>4</v>
@@ -21326,7 +21342,7 @@
       <c r="E25" s="58"/>
       <c r="F25" s="59">
         <f ca="1">F24+3</f>
-        <v>46046</v>
+        <v>46053</v>
       </c>
       <c r="G25" s="60">
         <v>14</v>
@@ -21569,7 +21585,7 @@
       <c r="E26" s="58"/>
       <c r="F26" s="59">
         <f ca="1">F25+15</f>
-        <v>46061</v>
+        <v>46068</v>
       </c>
       <c r="G26" s="60">
         <v>6</v>
@@ -21812,7 +21828,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="59">
         <f ca="1">F21+22</f>
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="G27" s="60">
         <v>3</v>
@@ -22055,7 +22071,7 @@
       <c r="E28" s="58"/>
       <c r="F28" s="59">
         <f ca="1">F16</f>
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="G28" s="60">
         <v>19</v>
@@ -22532,7 +22548,7 @@
       <c r="E30" s="58"/>
       <c r="F30" s="59">
         <f ca="1">F27+3</f>
-        <v>46068</v>
+        <v>46075</v>
       </c>
       <c r="G30" s="60">
         <v>15</v>
@@ -22773,7 +22789,7 @@
       <c r="E31" s="58"/>
       <c r="F31" s="59">
         <f ca="1">F30+14</f>
-        <v>46082</v>
+        <v>46089</v>
       </c>
       <c r="G31" s="60">
         <v>5</v>
@@ -23016,7 +23032,7 @@
       <c r="E32" s="58"/>
       <c r="F32" s="59">
         <f ca="1">F31+42</f>
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="G32" s="60">
         <v>1</v>
@@ -24479,15 +24495,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -24505,6 +24512,15 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24529,14 +24545,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAF2F40C-D12E-4644-AA6E-31E499F048DC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CD6AD73-D703-40CF-AB8D-72E6A3921BEB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -24546,4 +24554,12 @@
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAF2F40C-D12E-4644-AA6E-31E499F048DC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Diagramme/SmartClock_Gantt-Diagramm_V2.xlsx
+++ b/Diagramme/SmartClock_Gantt-Diagramm_V2.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
   <xr:revisionPtr revIDLastSave="697" documentId="8_{0C4EAEB1-A5C4-4402-980F-B32D81185735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64EE4A6D-F461-4C5D-B572-20DCEA631B00}"/>
   <bookViews>
@@ -259,7 +259,7 @@
     <numFmt numFmtId="165" formatCode="d"/>
     <numFmt numFmtId="166" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1169,6 +1169,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="13" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1187,34 +1214,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1693,36 +1693,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -1834,6 +1804,36 @@
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
           <bgColor theme="1" tint="0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2174,7 +2174,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Meilensteine4352" displayName="Meilensteine4352" ref="B9:G36" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Meilensteine4352" displayName="Meilensteine4352" ref="B9:G36" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2184,12 +2184,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Meilensteinbeschreibung" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Kategorie" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Zeitaufwand in std" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Fortschritt" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Start" dataDxfId="36" dataCellStyle="Datum"/>
-    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Tage" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Meilensteinbeschreibung" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Kategorie" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Zeitaufwand in std" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Fortschritt" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Start" dataDxfId="32" dataCellStyle="Datum"/>
+    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Tage" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="Aufgabenliste" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -2201,7 +2201,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Meilensteine435" displayName="Meilensteine435" ref="B9:G36" totalsRowShown="0" headerRowDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Meilensteine435" displayName="Meilensteine435" ref="B9:G36" totalsRowShown="0" headerRowDxfId="42">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -2211,9 +2211,9 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Meilensteinbeschreibung" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Kategorie" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Aufwand Soll / Ist" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Meilensteinbeschreibung" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Kategorie" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Aufwand Soll / Ist" dataDxfId="39"/>
     <tableColumn id="4" xr3:uid="{62B00BEF-16BE-4692-B5E2-F287F680F2C1}" name="Fortschritt"/>
     <tableColumn id="5" xr3:uid="{D6D72902-F68F-4E59-A714-AFFF520C647A}" name="Start" dataCellStyle="Datum"/>
     <tableColumn id="6" xr3:uid="{93E698DE-286F-49ED-AA20-D0C843671DE8}" name="Tage"/>
@@ -2519,7 +2519,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="8" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="8" customWidth="1"/>
@@ -2528,17 +2528,17 @@
     <col min="7" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" ht="28.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" s="7" customFormat="1" ht="28.5">
       <c r="D1" s="104"/>
     </row>
-    <row r="2" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" ht="50.1" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" s="110"/>
-      <c r="C2" s="124" t="s">
+      <c r="C2" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
       <c r="F2" s="110"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -2548,7 +2548,7 @@
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
     </row>
-    <row r="3" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" ht="14.45" customHeight="1">
       <c r="A3" s="7"/>
       <c r="B3" s="105"/>
       <c r="C3" s="106"/>
@@ -2563,14 +2563,14 @@
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
     </row>
-    <row r="4" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1">
       <c r="A4" s="7"/>
       <c r="B4" s="105"/>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="125"/>
-      <c r="E4" s="125"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
       <c r="F4" s="105"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -2580,14 +2580,14 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" s="8" customFormat="1" ht="75" customHeight="1">
       <c r="A5" s="7"/>
       <c r="B5" s="105"/>
-      <c r="C5" s="125" t="s">
+      <c r="C5" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
       <c r="F5" s="105"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -2597,7 +2597,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="15">
       <c r="A6" s="6"/>
       <c r="B6" s="108"/>
       <c r="C6" s="108"/>
@@ -2605,15 +2605,15 @@
       <c r="E6" s="108"/>
       <c r="F6" s="108"/>
     </row>
-    <row r="7" spans="1:13" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="50.1" customHeight="1">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
     </row>
-    <row r="8" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="14.45" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
     </row>
-    <row r="9" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="90" customHeight="1">
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -2621,51 +2621,51 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="14.45" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="D18" s="8"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="D19" s="8"/>
@@ -2688,7 +2688,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
     <col min="2" max="2" width="37.85546875" customWidth="1"/>
@@ -2702,30 +2702,30 @@
     <col min="65" max="65" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" ht="25.15" customHeight="1"/>
+    <row r="2" spans="1:68" ht="49.9" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="129"/>
-      <c r="S2" s="129"/>
-      <c r="T2" s="129"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="137"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
       <c r="U2" s="64"/>
       <c r="V2" s="64"/>
       <c r="W2" s="64"/>
@@ -2772,7 +2772,7 @@
       <c r="BL2" s="64"/>
       <c r="BM2" s="64"/>
     </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="65"/>
       <c r="C3" s="66"/>
@@ -2786,7 +2786,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" ht="30" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="69" t="s">
         <v>36</v>
@@ -2799,40 +2799,40 @@
         <v>30</v>
       </c>
       <c r="H4" s="72"/>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="131"/>
-      <c r="T4" s="131"/>
-      <c r="U4" s="131"/>
-      <c r="W4" s="131"/>
-      <c r="X4" s="131"/>
-      <c r="Y4" s="131"/>
-      <c r="Z4" s="131"/>
-      <c r="AA4" s="131"/>
-      <c r="AB4" s="131"/>
-      <c r="AD4" s="131"/>
-      <c r="AE4" s="131"/>
-      <c r="AF4" s="131"/>
-      <c r="AG4" s="131"/>
-      <c r="AH4" s="131"/>
-      <c r="AJ4" s="126"/>
-      <c r="AK4" s="126"/>
-      <c r="AL4" s="126"/>
-      <c r="AM4" s="126"/>
-      <c r="AN4" s="126"/>
-      <c r="AO4" s="126"/>
-      <c r="AP4" s="126"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="129"/>
+      <c r="P4" s="139"/>
+      <c r="Q4" s="139"/>
+      <c r="R4" s="139"/>
+      <c r="S4" s="139"/>
+      <c r="T4" s="139"/>
+      <c r="U4" s="139"/>
+      <c r="W4" s="139"/>
+      <c r="X4" s="139"/>
+      <c r="Y4" s="139"/>
+      <c r="Z4" s="139"/>
+      <c r="AA4" s="139"/>
+      <c r="AB4" s="139"/>
+      <c r="AD4" s="139"/>
+      <c r="AE4" s="139"/>
+      <c r="AF4" s="139"/>
+      <c r="AG4" s="139"/>
+      <c r="AH4" s="139"/>
+      <c r="AJ4" s="135"/>
+      <c r="AK4" s="135"/>
+      <c r="AL4" s="135"/>
+      <c r="AM4" s="135"/>
+      <c r="AN4" s="135"/>
+      <c r="AO4" s="135"/>
+      <c r="AP4" s="135"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" ht="30" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
@@ -2846,7 +2846,7 @@
       <c r="G5" s="72"/>
       <c r="H5" s="72"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:68" ht="30" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="76" t="s">
         <v>6</v>
@@ -2940,7 +2940,7 @@
       <c r="BK6" s="87"/>
       <c r="BL6" s="87"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" ht="30" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="76" t="s">
         <v>7</v>
@@ -3178,7 +3178,7 @@
         <v>46021</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="71"/>
       <c r="C8" s="71"/>
@@ -3244,7 +3244,7 @@
       <c r="BK8" s="99"/>
       <c r="BL8" s="102"/>
     </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" ht="40.15" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>D</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1">
       <c r="B10" s="16"/>
       <c r="C10" s="13"/>
       <c r="D10" s="12"/>
@@ -3556,7 +3556,7 @@
       <c r="BK10" s="34"/>
       <c r="BL10" s="34"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="123" t="s">
         <v>43</v>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="BP11" s="39"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="123"/>
       <c r="C12" s="57" t="s">
@@ -4043,7 +4043,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="123" t="s">
         <v>44</v>
@@ -4287,7 +4287,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="123"/>
       <c r="C14" s="57" t="s">
@@ -4529,7 +4529,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="123" t="s">
         <v>45</v>
@@ -4773,7 +4773,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="123"/>
       <c r="C16" s="57" t="s">
@@ -5015,7 +5015,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="123" t="s">
         <v>46</v>
@@ -5259,7 +5259,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="123"/>
       <c r="C18" s="57" t="s">
@@ -5501,7 +5501,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="123" t="s">
         <v>47</v>
@@ -5745,7 +5745,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A20" s="9"/>
       <c r="B20" s="123"/>
       <c r="C20" s="57" t="s">
@@ -5987,7 +5987,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="123" t="s">
         <v>48</v>
@@ -6231,7 +6231,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="123"/>
       <c r="C22" s="57" t="s">
@@ -6473,7 +6473,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="123" t="s">
         <v>49</v>
@@ -6709,7 +6709,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="123"/>
       <c r="C24" s="57"/>
@@ -6943,7 +6943,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="123" t="s">
         <v>50</v>
@@ -7179,7 +7179,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="123"/>
       <c r="C26" s="57"/>
@@ -7413,7 +7413,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="123" t="s">
         <v>51</v>
@@ -7649,7 +7649,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A28" s="9"/>
       <c r="B28" s="61"/>
       <c r="C28" s="57"/>
@@ -7883,7 +7883,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="113"/>
       <c r="C29" s="57"/>
@@ -8117,7 +8117,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="61"/>
       <c r="C30" s="57"/>
@@ -8351,7 +8351,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A31" s="9"/>
       <c r="B31" s="61"/>
       <c r="C31" s="57"/>
@@ -8585,7 +8585,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="61"/>
       <c r="C32" s="57"/>
@@ -8819,7 +8819,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="61"/>
       <c r="C33" s="57"/>
@@ -9053,7 +9053,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="61"/>
       <c r="C34" s="57"/>
@@ -9287,7 +9287,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="61"/>
       <c r="C35" s="57"/>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="BM35" s="86"/>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A36" s="10"/>
       <c r="B36" s="115" t="s">
         <v>18</v>
@@ -9590,12 +9590,12 @@
       <c r="BK36" s="84"/>
       <c r="BL36" s="84"/>
     </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" ht="30" customHeight="1">
       <c r="D37" s="4"/>
       <c r="G37" s="11"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" ht="30" customHeight="1">
       <c r="D38" s="5"/>
     </row>
   </sheetData>
@@ -9755,7 +9755,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
     <col min="2" max="2" width="37.85546875" customWidth="1"/>
@@ -9769,30 +9769,30 @@
     <col min="65" max="65" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" ht="25.15" customHeight="1"/>
+    <row r="2" spans="1:68" ht="49.9" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="134"/>
-      <c r="L2" s="134"/>
-      <c r="M2" s="134"/>
-      <c r="N2" s="134"/>
-      <c r="O2" s="135"/>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="136"/>
-      <c r="R2" s="136"/>
-      <c r="S2" s="136"/>
-      <c r="T2" s="136"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
+      <c r="M2" s="126"/>
+      <c r="N2" s="126"/>
+      <c r="O2" s="127"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
+      <c r="R2" s="128"/>
+      <c r="S2" s="128"/>
+      <c r="T2" s="128"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
       <c r="W2" s="20"/>
@@ -9839,7 +9839,7 @@
       <c r="BL2" s="20"/>
       <c r="BM2" s="20"/>
     </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="40"/>
       <c r="C3" s="41"/>
@@ -9906,7 +9906,7 @@
       <c r="BL3" s="30"/>
       <c r="BM3" s="30"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" ht="30" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="52" t="s">
         <v>36</v>
@@ -9919,50 +9919,50 @@
         <v>30</v>
       </c>
       <c r="H4" s="27"/>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="129"/>
       <c r="O4" s="30"/>
-      <c r="P4" s="137" t="s">
+      <c r="P4" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
+      <c r="S4" s="130"/>
+      <c r="T4" s="130"/>
+      <c r="U4" s="130"/>
       <c r="V4" s="30"/>
-      <c r="W4" s="138" t="s">
+      <c r="W4" s="131" t="s">
         <v>33</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="138"/>
-      <c r="Z4" s="138"/>
-      <c r="AA4" s="138"/>
-      <c r="AB4" s="138"/>
+      <c r="X4" s="131"/>
+      <c r="Y4" s="131"/>
+      <c r="Z4" s="131"/>
+      <c r="AA4" s="131"/>
+      <c r="AB4" s="131"/>
       <c r="AC4" s="30"/>
-      <c r="AD4" s="139" t="s">
+      <c r="AD4" s="132" t="s">
         <v>33</v>
       </c>
-      <c r="AE4" s="139"/>
-      <c r="AF4" s="139"/>
-      <c r="AG4" s="139"/>
-      <c r="AH4" s="139"/>
+      <c r="AE4" s="132"/>
+      <c r="AF4" s="132"/>
+      <c r="AG4" s="132"/>
+      <c r="AH4" s="132"/>
       <c r="AI4" s="30"/>
-      <c r="AJ4" s="132" t="s">
+      <c r="AJ4" s="124" t="s">
         <v>33</v>
       </c>
-      <c r="AK4" s="132"/>
-      <c r="AL4" s="132"/>
-      <c r="AM4" s="132"/>
-      <c r="AN4" s="132"/>
-      <c r="AO4" s="132"/>
-      <c r="AP4" s="132"/>
+      <c r="AK4" s="124"/>
+      <c r="AL4" s="124"/>
+      <c r="AM4" s="124"/>
+      <c r="AN4" s="124"/>
+      <c r="AO4" s="124"/>
+      <c r="AP4" s="124"/>
       <c r="AQ4" s="30"/>
       <c r="AR4" s="30"/>
       <c r="AS4" s="30"/>
@@ -9987,7 +9987,7 @@
       <c r="BL4" s="30"/>
       <c r="BM4" s="30"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" ht="30" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
@@ -10058,7 +10058,7 @@
       <c r="BL5" s="30"/>
       <c r="BM5" s="30"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:68" ht="30" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="47" t="s">
         <v>6</v>
@@ -10153,7 +10153,7 @@
       <c r="BL6" s="63"/>
       <c r="BM6" s="30"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" ht="30" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="47" t="s">
         <v>7</v>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="BM7" s="30"/>
     </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="49"/>
       <c r="C8" s="49"/>
@@ -10459,7 +10459,7 @@
       <c r="BL8" s="37"/>
       <c r="BM8" s="30"/>
     </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" ht="40.15" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="BM9" s="30"/>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1">
       <c r="B10" s="16"/>
       <c r="C10" s="13"/>
       <c r="D10" s="12"/>
@@ -10774,7 +10774,7 @@
       <c r="BL10" s="34"/>
       <c r="BM10" s="30"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="120" t="s">
         <v>38</v>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="BP11" s="39"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="121" t="s">
         <v>53</v>
@@ -11261,7 +11261,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="121"/>
       <c r="C13" s="21" t="s">
@@ -11505,7 +11505,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="121" t="s">
         <v>54</v>
@@ -11751,7 +11751,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="121"/>
       <c r="C15" s="21" t="s">
@@ -11995,7 +11995,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="121" t="s">
         <v>55</v>
@@ -12241,7 +12241,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="121"/>
       <c r="C17" s="21" t="s">
@@ -12485,7 +12485,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="121" t="s">
         <v>56</v>
@@ -12731,7 +12731,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="12"/>
       <c r="C19" s="21" t="s">
@@ -12975,7 +12975,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A20" s="9"/>
       <c r="B20" s="121" t="s">
         <v>57</v>
@@ -13221,7 +13221,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="121"/>
       <c r="C21" s="21" t="s">
@@ -13461,7 +13461,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="121"/>
       <c r="C22" s="21" t="s">
@@ -13701,7 +13701,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="121"/>
       <c r="C23" s="21" t="s">
@@ -13941,7 +13941,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="121"/>
       <c r="C24" s="21" t="s">
@@ -14181,7 +14181,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="121"/>
       <c r="C25" s="21" t="s">
@@ -14421,7 +14421,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="121"/>
       <c r="C26" s="21" t="s">
@@ -14661,7 +14661,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="121"/>
       <c r="C27" s="21" t="s">
@@ -14901,7 +14901,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A28" s="9"/>
       <c r="B28" s="12"/>
       <c r="C28" s="21" t="s">
@@ -15141,7 +15141,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="121"/>
       <c r="C29" s="21" t="s">
@@ -15381,7 +15381,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="121"/>
       <c r="C30" s="21" t="s">
@@ -15621,7 +15621,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A31" s="9"/>
       <c r="B31" s="121"/>
       <c r="C31" s="21" t="s">
@@ -15861,7 +15861,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="121"/>
       <c r="C32" s="21" t="s">
@@ -16101,7 +16101,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="121"/>
       <c r="C33" s="21" t="s">
@@ -16341,7 +16341,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="121"/>
       <c r="C34" s="21" t="s">
@@ -16581,7 +16581,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="121"/>
       <c r="C35" s="21" t="s">
@@ -16821,7 +16821,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A36" s="10"/>
       <c r="B36" s="114" t="s">
         <v>18</v>
@@ -16890,12 +16890,12 @@
       <c r="BL36" s="54"/>
       <c r="BM36" s="26"/>
     </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" ht="30" customHeight="1">
       <c r="D37" s="4"/>
       <c r="G37" s="11"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" ht="30" customHeight="1">
       <c r="D38" s="5"/>
     </row>
   </sheetData>
@@ -17059,7 +17059,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="9" customWidth="1"/>
     <col min="2" max="2" width="37.85546875" customWidth="1"/>
@@ -17073,8 +17073,8 @@
     <col min="65" max="65" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" ht="25.15" customHeight="1"/>
+    <row r="2" spans="1:68" ht="49.9" customHeight="1">
       <c r="A2" s="10"/>
       <c r="B2" s="140" t="s">
         <v>3</v>
@@ -17143,7 +17143,7 @@
       <c r="BL2" s="94"/>
       <c r="BM2" s="94"/>
     </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="65"/>
       <c r="C3" s="66"/>
@@ -17157,7 +17157,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" ht="30" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="69" t="s">
         <v>4</v>
@@ -17170,48 +17170,48 @@
         <v>30</v>
       </c>
       <c r="H4" s="72"/>
-      <c r="I4" s="130" t="s">
+      <c r="I4" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="P4" s="137" t="s">
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="129"/>
+      <c r="P4" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137"/>
-      <c r="W4" s="138" t="s">
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
+      <c r="S4" s="130"/>
+      <c r="T4" s="130"/>
+      <c r="U4" s="130"/>
+      <c r="W4" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="X4" s="138"/>
-      <c r="Y4" s="138"/>
-      <c r="Z4" s="138"/>
-      <c r="AA4" s="138"/>
-      <c r="AB4" s="138"/>
-      <c r="AD4" s="139" t="s">
+      <c r="X4" s="131"/>
+      <c r="Y4" s="131"/>
+      <c r="Z4" s="131"/>
+      <c r="AA4" s="131"/>
+      <c r="AB4" s="131"/>
+      <c r="AD4" s="132" t="s">
         <v>32</v>
       </c>
-      <c r="AE4" s="139"/>
-      <c r="AF4" s="139"/>
-      <c r="AG4" s="139"/>
-      <c r="AH4" s="139"/>
-      <c r="AJ4" s="132" t="s">
+      <c r="AE4" s="132"/>
+      <c r="AF4" s="132"/>
+      <c r="AG4" s="132"/>
+      <c r="AH4" s="132"/>
+      <c r="AJ4" s="124" t="s">
         <v>33</v>
       </c>
-      <c r="AK4" s="132"/>
-      <c r="AL4" s="132"/>
-      <c r="AM4" s="132"/>
-      <c r="AN4" s="132"/>
-      <c r="AO4" s="132"/>
-      <c r="AP4" s="132"/>
+      <c r="AK4" s="124"/>
+      <c r="AL4" s="124"/>
+      <c r="AM4" s="124"/>
+      <c r="AN4" s="124"/>
+      <c r="AO4" s="124"/>
+      <c r="AP4" s="124"/>
     </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" ht="30" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
@@ -17225,14 +17225,14 @@
       <c r="G5" s="72"/>
       <c r="H5" s="72"/>
     </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:68" ht="30" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="76" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="77" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">IFERROR(IF(MIN(Meilensteine43524[Start])=0,TODAY(),B11(Meilensteine43524[Start])),TODAY())</f>
-        <v>46035</v>
+        <v>46070</v>
       </c>
       <c r="D6" s="78"/>
       <c r="E6" s="72"/>
@@ -17241,7 +17241,7 @@
       <c r="H6" s="72"/>
       <c r="I6" s="88" t="str">
         <f ca="1">TEXT(I7,"MMMM")</f>
-        <v>Januar</v>
+        <v>Februar</v>
       </c>
       <c r="J6" s="88"/>
       <c r="K6" s="88"/>
@@ -17261,7 +17261,7 @@
       <c r="V6" s="88"/>
       <c r="W6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(W7,"MMMM")=P6,TEXT(W7,"MMMM")=I6),"",TEXT(W7,"MMMM"))</f>
-        <v/>
+        <v>März</v>
       </c>
       <c r="X6" s="88"/>
       <c r="Y6" s="88"/>
@@ -17271,7 +17271,7 @@
       <c r="AC6" s="88"/>
       <c r="AD6" s="88" t="str">
         <f ca="1">IF(OR(TEXT(AD7,"MMMM")=W6,TEXT(AD7,"MMMM")=P6,TEXT(AD7,"MMMM")=I6),"",TEXT(AD7,"MMMM"))</f>
-        <v>Februar</v>
+        <v/>
       </c>
       <c r="AE6" s="88"/>
       <c r="AF6" s="88"/>
@@ -17301,7 +17301,7 @@
       <c r="AX6" s="89"/>
       <c r="AY6" s="89" t="str">
         <f ca="1">IF(OR(TEXT(AY7,"MMMM")=AR6,TEXT(AY7,"MMMM")=AK6,TEXT(AY7,"MMMM")=AD6,TEXT(AY7,"MMMM")=W6),"",TEXT(AY7,"MMMM"))</f>
-        <v/>
+        <v>April</v>
       </c>
       <c r="AZ6" s="89"/>
       <c r="BA6" s="89"/>
@@ -17311,7 +17311,7 @@
       <c r="BE6" s="87"/>
       <c r="BF6" s="87" t="str">
         <f ca="1">IF(OR(TEXT(BF7,"MMMM")=AY6,TEXT(BF7,"MMMM")=AR6,TEXT(BF7,"MMMM")=AK6,TEXT(BF7,"MMMM")=AD6),"",TEXT(BF7,"MMMM"))</f>
-        <v>März</v>
+        <v/>
       </c>
       <c r="BG6" s="87"/>
       <c r="BH6" s="87"/>
@@ -17320,7 +17320,7 @@
       <c r="BK6" s="87"/>
       <c r="BL6" s="87"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" ht="30" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="76" t="s">
         <v>7</v>
@@ -17335,230 +17335,230 @@
       <c r="H7" s="80"/>
       <c r="I7" s="95">
         <f ca="1">IFERROR(Projekt_Start+Scrollschrittweite,TODAY())</f>
-        <v>46036</v>
+        <v>46071</v>
       </c>
       <c r="J7" s="96">
         <f ca="1">I7+1</f>
-        <v>46037</v>
+        <v>46072</v>
       </c>
       <c r="K7" s="96">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46038</v>
+        <v>46073</v>
       </c>
       <c r="L7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46039</v>
+        <v>46074</v>
       </c>
       <c r="M7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46040</v>
+        <v>46075</v>
       </c>
       <c r="N7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46041</v>
+        <v>46076</v>
       </c>
       <c r="O7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46042</v>
+        <v>46077</v>
       </c>
       <c r="P7" s="96">
         <f ca="1">O7+1</f>
-        <v>46043</v>
+        <v>46078</v>
       </c>
       <c r="Q7" s="96">
         <f ca="1">P7+1</f>
-        <v>46044</v>
+        <v>46079</v>
       </c>
       <c r="R7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46045</v>
+        <v>46080</v>
       </c>
       <c r="S7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46046</v>
+        <v>46081</v>
       </c>
       <c r="T7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46047</v>
+        <v>46082</v>
       </c>
       <c r="U7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46048</v>
+        <v>46083</v>
       </c>
       <c r="V7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46049</v>
+        <v>46084</v>
       </c>
       <c r="W7" s="96">
         <f ca="1">V7+1</f>
-        <v>46050</v>
+        <v>46085</v>
       </c>
       <c r="X7" s="96">
         <f ca="1">W7+1</f>
-        <v>46051</v>
+        <v>46086</v>
       </c>
       <c r="Y7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46052</v>
+        <v>46087</v>
       </c>
       <c r="Z7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46053</v>
+        <v>46088</v>
       </c>
       <c r="AA7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46054</v>
+        <v>46089</v>
       </c>
       <c r="AB7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46055</v>
+        <v>46090</v>
       </c>
       <c r="AC7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46056</v>
+        <v>46091</v>
       </c>
       <c r="AD7" s="96">
         <f ca="1">AC7+1</f>
-        <v>46057</v>
+        <v>46092</v>
       </c>
       <c r="AE7" s="96">
         <f ca="1">AD7+1</f>
-        <v>46058</v>
+        <v>46093</v>
       </c>
       <c r="AF7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46059</v>
+        <v>46094</v>
       </c>
       <c r="AG7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46060</v>
+        <v>46095</v>
       </c>
       <c r="AH7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46061</v>
+        <v>46096</v>
       </c>
       <c r="AI7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46062</v>
+        <v>46097</v>
       </c>
       <c r="AJ7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46063</v>
+        <v>46098</v>
       </c>
       <c r="AK7" s="96">
         <f ca="1">AJ7+1</f>
-        <v>46064</v>
+        <v>46099</v>
       </c>
       <c r="AL7" s="96">
         <f ca="1">AK7+1</f>
-        <v>46065</v>
+        <v>46100</v>
       </c>
       <c r="AM7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46066</v>
+        <v>46101</v>
       </c>
       <c r="AN7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46067</v>
+        <v>46102</v>
       </c>
       <c r="AO7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46068</v>
+        <v>46103</v>
       </c>
       <c r="AP7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46069</v>
+        <v>46104</v>
       </c>
       <c r="AQ7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46070</v>
+        <v>46105</v>
       </c>
       <c r="AR7" s="96">
         <f ca="1">AQ7+1</f>
-        <v>46071</v>
+        <v>46106</v>
       </c>
       <c r="AS7" s="96">
         <f ca="1">AR7+1</f>
-        <v>46072</v>
+        <v>46107</v>
       </c>
       <c r="AT7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46073</v>
+        <v>46108</v>
       </c>
       <c r="AU7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46074</v>
+        <v>46109</v>
       </c>
       <c r="AV7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46075</v>
+        <v>46110</v>
       </c>
       <c r="AW7" s="96">
         <f t="shared" ca="1" si="0"/>
-        <v>46076</v>
+        <v>46111</v>
       </c>
       <c r="AX7" s="97">
         <f t="shared" ca="1" si="0"/>
-        <v>46077</v>
+        <v>46112</v>
       </c>
       <c r="AY7" s="96">
         <f ca="1">AX7+1</f>
-        <v>46078</v>
+        <v>46113</v>
       </c>
       <c r="AZ7" s="96">
         <f ca="1">AY7+1</f>
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="BA7" s="96">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46080</v>
+        <v>46115</v>
       </c>
       <c r="BB7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46081</v>
+        <v>46116</v>
       </c>
       <c r="BC7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46082</v>
+        <v>46117</v>
       </c>
       <c r="BD7" s="96">
         <f t="shared" ca="1" si="1"/>
-        <v>46083</v>
+        <v>46118</v>
       </c>
       <c r="BE7" s="97">
         <f t="shared" ca="1" si="1"/>
-        <v>46084</v>
+        <v>46119</v>
       </c>
       <c r="BF7" s="96">
         <f ca="1">BE7+1</f>
-        <v>46085</v>
+        <v>46120</v>
       </c>
       <c r="BG7" s="96">
         <f ca="1">BF7+1</f>
-        <v>46086</v>
+        <v>46121</v>
       </c>
       <c r="BH7" s="96">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46087</v>
+        <v>46122</v>
       </c>
       <c r="BI7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46088</v>
+        <v>46123</v>
       </c>
       <c r="BJ7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46089</v>
+        <v>46124</v>
       </c>
       <c r="BK7" s="96">
         <f t="shared" ca="1" si="2"/>
-        <v>46090</v>
+        <v>46125</v>
       </c>
       <c r="BL7" s="97">
         <f t="shared" ca="1" si="2"/>
-        <v>46091</v>
+        <v>46126</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="71"/>
       <c r="C8" s="71"/>
@@ -17624,7 +17624,7 @@
       <c r="BK8" s="99"/>
       <c r="BL8" s="102"/>
     </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" ht="40.15" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>35</v>
       </c>
@@ -17872,7 +17872,7 @@
         <v>D</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1">
       <c r="B10" s="16"/>
       <c r="C10" s="13"/>
       <c r="D10" s="12"/>
@@ -17936,7 +17936,7 @@
       <c r="BK10" s="34"/>
       <c r="BL10" s="34"/>
     </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="113" t="s">
         <v>9</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="BP11" s="39"/>
     </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="61" t="s">
         <v>10</v>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="F12" s="59">
         <f ca="1">TODAY()</f>
-        <v>46035</v>
+        <v>46070</v>
       </c>
       <c r="G12" s="60">
         <v>3</v>
@@ -18420,7 +18420,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="61" t="s">
         <v>11</v>
@@ -18432,7 +18432,7 @@
       <c r="E13" s="58"/>
       <c r="F13" s="59">
         <f ca="1">TODAY()+5</f>
-        <v>46040</v>
+        <v>46075</v>
       </c>
       <c r="G13" s="60">
         <v>1</v>
@@ -18663,7 +18663,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A14" s="9"/>
       <c r="B14" s="61" t="s">
         <v>12</v>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="F14" s="59">
         <f ca="1">F12-3</f>
-        <v>46032</v>
+        <v>46067</v>
       </c>
       <c r="G14" s="60">
         <v>10</v>
@@ -18908,7 +18908,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="61" t="s">
         <v>13</v>
@@ -18920,7 +18920,7 @@
       <c r="E15" s="58"/>
       <c r="F15" s="59">
         <f ca="1">F12+20</f>
-        <v>46055</v>
+        <v>46090</v>
       </c>
       <c r="G15" s="60">
         <v>1</v>
@@ -19151,7 +19151,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="61" t="s">
         <v>14</v>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="F16" s="59">
         <f ca="1">F12+6</f>
-        <v>46041</v>
+        <v>46076</v>
       </c>
       <c r="G16" s="60">
         <v>6</v>
@@ -19396,7 +19396,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="113" t="s">
         <v>15</v>
@@ -19632,7 +19632,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="61" t="s">
         <v>10</v>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="F18" s="59">
         <f ca="1">F12+6</f>
-        <v>46041</v>
+        <v>46076</v>
       </c>
       <c r="G18" s="60">
         <v>13</v>
@@ -19877,7 +19877,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="61" t="s">
         <v>11</v>
@@ -19891,7 +19891,7 @@
       </c>
       <c r="F19" s="59">
         <f ca="1">F18+2</f>
-        <v>46043</v>
+        <v>46078</v>
       </c>
       <c r="G19" s="60">
         <v>9</v>
@@ -20122,7 +20122,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A20" s="9"/>
       <c r="B20" s="61" t="s">
         <v>12</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="F20" s="59">
         <f ca="1">F19+5</f>
-        <v>46048</v>
+        <v>46083</v>
       </c>
       <c r="G20" s="60">
         <v>11</v>
@@ -20367,7 +20367,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="61" t="s">
         <v>13</v>
@@ -20379,7 +20379,7 @@
       <c r="E21" s="58"/>
       <c r="F21" s="59">
         <f ca="1">F20+2</f>
-        <v>46050</v>
+        <v>46085</v>
       </c>
       <c r="G21" s="60">
         <v>1</v>
@@ -20610,7 +20610,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="61" t="s">
         <v>14</v>
@@ -20620,7 +20620,7 @@
       <c r="E22" s="58"/>
       <c r="F22" s="59">
         <f ca="1">F21+1</f>
-        <v>46051</v>
+        <v>46086</v>
       </c>
       <c r="G22" s="60">
         <v>24</v>
@@ -20851,7 +20851,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="113" t="s">
         <v>16</v>
@@ -21087,7 +21087,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="61" t="s">
         <v>10</v>
@@ -21099,7 +21099,7 @@
       <c r="E24" s="58"/>
       <c r="F24" s="59">
         <f ca="1">F12+15</f>
-        <v>46050</v>
+        <v>46085</v>
       </c>
       <c r="G24" s="60">
         <v>4</v>
@@ -21330,7 +21330,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="61" t="s">
         <v>11</v>
@@ -21342,7 +21342,7 @@
       <c r="E25" s="58"/>
       <c r="F25" s="59">
         <f ca="1">F24+3</f>
-        <v>46053</v>
+        <v>46088</v>
       </c>
       <c r="G25" s="60">
         <v>14</v>
@@ -21573,7 +21573,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="61" t="s">
         <v>12</v>
@@ -21585,7 +21585,7 @@
       <c r="E26" s="58"/>
       <c r="F26" s="59">
         <f ca="1">F25+15</f>
-        <v>46068</v>
+        <v>46103</v>
       </c>
       <c r="G26" s="60">
         <v>6</v>
@@ -21816,7 +21816,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="61" t="s">
         <v>13</v>
@@ -21828,7 +21828,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="59">
         <f ca="1">F21+22</f>
-        <v>46072</v>
+        <v>46107</v>
       </c>
       <c r="G27" s="60">
         <v>3</v>
@@ -22059,7 +22059,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A28" s="9"/>
       <c r="B28" s="61" t="s">
         <v>14</v>
@@ -22071,7 +22071,7 @@
       <c r="E28" s="58"/>
       <c r="F28" s="59">
         <f ca="1">F16</f>
-        <v>46041</v>
+        <v>46076</v>
       </c>
       <c r="G28" s="60">
         <v>19</v>
@@ -22302,7 +22302,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="113" t="s">
         <v>17</v>
@@ -22538,7 +22538,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="61" t="s">
         <v>10</v>
@@ -22548,7 +22548,7 @@
       <c r="E30" s="58"/>
       <c r="F30" s="59">
         <f ca="1">F27+3</f>
-        <v>46075</v>
+        <v>46110</v>
       </c>
       <c r="G30" s="60">
         <v>15</v>
@@ -22779,7 +22779,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A31" s="9"/>
       <c r="B31" s="61" t="s">
         <v>11</v>
@@ -22789,7 +22789,7 @@
       <c r="E31" s="58"/>
       <c r="F31" s="59">
         <f ca="1">F30+14</f>
-        <v>46089</v>
+        <v>46124</v>
       </c>
       <c r="G31" s="60">
         <v>5</v>
@@ -23020,7 +23020,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="61" t="s">
         <v>12</v>
@@ -23032,7 +23032,7 @@
       <c r="E32" s="58"/>
       <c r="F32" s="59">
         <f ca="1">F31+42</f>
-        <v>46131</v>
+        <v>46166</v>
       </c>
       <c r="G32" s="60">
         <v>1</v>
@@ -23263,7 +23263,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="61" t="s">
         <v>13</v>
@@ -23499,7 +23499,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="61" t="s">
         <v>14</v>
@@ -23735,7 +23735,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="61"/>
       <c r="C35" s="57"/>
@@ -23970,7 +23970,7 @@
       </c>
       <c r="BM35" s="86"/>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1">
       <c r="A36" s="10"/>
       <c r="B36" s="115" t="s">
         <v>18</v>
@@ -24038,12 +24038,12 @@
       <c r="BK36" s="84"/>
       <c r="BL36" s="84"/>
     </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:65" ht="30" customHeight="1">
       <c r="D37" s="4"/>
       <c r="G37" s="11"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:65" ht="30" customHeight="1">
       <c r="D38" s="5"/>
     </row>
   </sheetData>
@@ -24495,6 +24495,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -24512,15 +24521,6 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24545,6 +24545,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAF2F40C-D12E-4644-AA6E-31E499F048DC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CD6AD73-D703-40CF-AB8D-72E6A3921BEB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -24554,12 +24562,4 @@
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAF2F40C-D12E-4644-AA6E-31E499F048DC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>